--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_26aug26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_26aug26_Wed.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AVITA\projects\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CC605D-6A55-46AD-89FB-F96891BD36D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet1 (2)'!$A$1:$O$267</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$L$21</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -700,7 +699,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1317,28 +1316,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O267"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="13"/>
-    <col min="4" max="5" width="8.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="13"/>
-    <col min="10" max="10" width="10.54296875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="13"/>
+    <col min="4" max="5" width="8.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="13"/>
+    <col min="10" max="10" width="10.5546875" style="21" customWidth="1"/>
     <col min="11" max="11" width="19" style="21" customWidth="1"/>
-    <col min="12" max="13" width="8.90625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.81640625" style="13"/>
-    <col min="15" max="15" width="8.81640625" style="21"/>
-    <col min="16" max="16384" width="8.81640625" style="13"/>
+    <col min="12" max="13" width="8.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="13"/>
+    <col min="15" max="15" width="8.77734375" style="21"/>
+    <col min="16" max="16384" width="8.77734375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1379,7 +1377,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>46252.6875</v>
       </c>
@@ -1414,12 +1412,12 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B2, $C$2:$C$911, C2, $D$2:$D$911, D2, $E$2:$E$911, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$911, B2, $C$2:$C$911, C2, $D$2:$D$911, D2, $E$2:$E$911, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>46260.375543981485</v>
       </c>
@@ -1461,12 +1459,12 @@
         <v>10680</v>
       </c>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B3, $C$2:$C$911, C3, $D$2:$D$911, D3, $E$2:$E$911, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="21"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1499,12 +1497,12 @@
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B4, $C$2:$C$911, C4, $D$2:$D$911, D4, $E$2:$E$911, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>46252.6875</v>
       </c>
@@ -1539,12 +1537,12 @@
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B5, $C$2:$C$911, C5, $D$2:$D$911, D5, $E$2:$E$911, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -1577,12 +1575,12 @@
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B6, $C$2:$C$911, C6, $D$2:$D$911, D6, $E$2:$E$911, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>46260.375509259262</v>
       </c>
@@ -1624,12 +1622,12 @@
         <v>460</v>
       </c>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B7, $C$2:$C$911, C7, $D$2:$D$911, D7, $E$2:$E$911, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O7" s="21"/>
     </row>
-    <row r="8" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>46260.375509259262</v>
       </c>
@@ -1671,12 +1669,12 @@
         <v>340</v>
       </c>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B8, $C$2:$C$911, C8, $D$2:$D$911, D8, $E$2:$E$911, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O8" s="21"/>
     </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -1711,12 +1709,12 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B9, $C$2:$C$911, C9, $D$2:$D$911, D9, $E$2:$E$911, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="20"/>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>46260.375543981485</v>
       </c>
@@ -1758,12 +1756,12 @@
         <v>10780</v>
       </c>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B10, $C$2:$C$911, C10, $D$2:$D$911, D10, $E$2:$E$911, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="21"/>
     </row>
-    <row r="11" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>46260.375509259262</v>
       </c>
@@ -1805,12 +1803,12 @@
         <v>300</v>
       </c>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B11, $C$2:$C$911, C11, $D$2:$D$911, D11, $E$2:$E$911, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="21"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>46252.6875</v>
       </c>
@@ -1845,12 +1843,12 @@
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B12, $C$2:$C$911, C12, $D$2:$D$911, D12, $E$2:$E$911, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="20"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>151</v>
       </c>
@@ -1887,12 +1885,12 @@
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B13, $C$2:$C$911, C13, $D$2:$D$911, D13, $E$2:$E$911, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="20"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -1927,12 +1925,12 @@
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B14, $C$2:$C$911, C14, $D$2:$D$911, D14, $E$2:$E$911, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="20"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1967,12 +1965,12 @@
       <c r="L15" s="20"/>
       <c r="M15" s="20"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B15, $C$2:$C$911, C15, $D$2:$D$911, D15, $E$2:$E$911, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="20"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -2005,12 +2003,12 @@
       <c r="L16" s="20"/>
       <c r="M16" s="20"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B16, $C$2:$C$911, C16, $D$2:$D$911, D16, $E$2:$E$911, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="20"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>46252.6875</v>
       </c>
@@ -2043,12 +2041,12 @@
       <c r="L17" s="20"/>
       <c r="M17" s="20"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B17, $C$2:$C$911, C17, $D$2:$D$911, D17, $E$2:$E$911, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="20"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -2090,12 +2088,12 @@
         <v>700</v>
       </c>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B18, $C$2:$C$911, C18, $D$2:$D$911, D18, $E$2:$E$911, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="21"/>
     </row>
-    <row r="19" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -2130,12 +2128,12 @@
       <c r="L19" s="20"/>
       <c r="M19" s="20"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B19, $C$2:$C$911, C19, $D$2:$D$911, D19, $E$2:$E$911, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="20"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>46252.6875</v>
       </c>
@@ -2168,12 +2166,12 @@
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B20, $C$2:$C$911, C20, $D$2:$D$911, D20, $E$2:$E$911, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="20"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>62</v>
       </c>
@@ -2208,12 +2206,12 @@
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B21, $C$2:$C$911, C21, $D$2:$D$911, D21, $E$2:$E$911, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="20"/>
     </row>
-    <row r="22" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2248,12 +2246,12 @@
       <c r="L22" s="20"/>
       <c r="M22" s="20"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B22, $C$2:$C$911, C22, $D$2:$D$911, D22, $E$2:$E$911, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="20"/>
     </row>
-    <row r="23" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>46254.375</v>
       </c>
@@ -2290,12 +2288,12 @@
       <c r="L23" s="20"/>
       <c r="M23" s="20"/>
       <c r="N23" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B23, $C$2:$C$911, C23, $D$2:$D$911, D23, $E$2:$E$911, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="20"/>
     </row>
-    <row r="24" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>46258.613194444442</v>
       </c>
@@ -2337,12 +2335,12 @@
         <v>300</v>
       </c>
       <c r="N24" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B24, $C$2:$C$911, C24, $D$2:$D$911, D24, $E$2:$E$911, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="21"/>
     </row>
-    <row r="25" spans="1:15" s="62" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" s="62" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="54">
         <v>46255</v>
       </c>
@@ -2384,12 +2382,12 @@
         <v>340</v>
       </c>
       <c r="N25" s="61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B25, $C$2:$C$911, C25, $D$2:$D$911, D25, $E$2:$E$911, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="60"/>
     </row>
-    <row r="26" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -2424,12 +2422,12 @@
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B26, $C$2:$C$911, C26, $D$2:$D$911, D26, $E$2:$E$911, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="20"/>
     </row>
-    <row r="27" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
@@ -2464,12 +2462,12 @@
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B27, $C$2:$C$911, C27, $D$2:$D$911, D27, $E$2:$E$911, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="20"/>
     </row>
-    <row r="28" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
@@ -2502,12 +2500,12 @@
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B28, $C$2:$C$911, C28, $D$2:$D$911, D28, $E$2:$E$911, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="20"/>
     </row>
-    <row r="29" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
@@ -2540,12 +2538,12 @@
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B29, $C$2:$C$911, C29, $D$2:$D$911, D29, $E$2:$E$911, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="20"/>
     </row>
-    <row r="30" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>46252.6875</v>
       </c>
@@ -2578,12 +2576,12 @@
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B30, $C$2:$C$911, C30, $D$2:$D$911, D30, $E$2:$E$911, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="20"/>
     </row>
-    <row r="31" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>46252.6875</v>
       </c>
@@ -2616,12 +2614,12 @@
       <c r="L31" s="20"/>
       <c r="M31" s="20"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B31, $C$2:$C$911, C31, $D$2:$D$911, D31, $E$2:$E$911, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="20"/>
     </row>
-    <row r="32" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>62</v>
       </c>
@@ -2656,12 +2654,12 @@
       <c r="L32" s="20"/>
       <c r="M32" s="20"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B32, $C$2:$C$911, C32, $D$2:$D$911, D32, $E$2:$E$911, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="20"/>
     </row>
-    <row r="33" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="23">
         <v>46255</v>
       </c>
@@ -2703,12 +2701,12 @@
         <v>300</v>
       </c>
       <c r="N33" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B33, $C$2:$C$911, C33, $D$2:$D$911, D33, $E$2:$E$911, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="21"/>
     </row>
-    <row r="34" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -2750,12 +2748,12 @@
         <v>5798</v>
       </c>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B34, $C$2:$C$911, C34, $D$2:$D$911, D34, $E$2:$E$911, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="21"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -2797,12 +2795,12 @@
         <v>750</v>
       </c>
       <c r="N35" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B35, $C$2:$C$911, C35, $D$2:$D$911, D35, $E$2:$E$911, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="21"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>62</v>
       </c>
@@ -2835,12 +2833,12 @@
       <c r="L36" s="20"/>
       <c r="M36" s="20"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B36, $C$2:$C$911, C36, $D$2:$D$911, D36, $E$2:$E$911, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="20"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -2873,12 +2871,12 @@
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B37, $C$2:$C$911, C37, $D$2:$D$911, D37, $E$2:$E$911, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="20"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -2915,12 +2913,12 @@
       <c r="L38" s="20"/>
       <c r="M38" s="20"/>
       <c r="N38" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B38, $C$2:$C$911, C38, $D$2:$D$911, D38, $E$2:$E$911, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="20"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23">
         <v>46255</v>
       </c>
@@ -2962,12 +2960,12 @@
         <v>300</v>
       </c>
       <c r="N39" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B39, $C$2:$C$911, C39, $D$2:$D$911, D39, $E$2:$E$911, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="21"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>46258.459722222222</v>
       </c>
@@ -3009,12 +3007,12 @@
         <v>295</v>
       </c>
       <c r="N40" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B40, $C$2:$C$911, C40, $D$2:$D$911, D40, $E$2:$E$911, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="21"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
@@ -3047,12 +3045,12 @@
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B41, $C$2:$C$911, C41, $D$2:$D$911, D41, $E$2:$E$911, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="20"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>46254.375</v>
       </c>
@@ -3089,12 +3087,12 @@
       <c r="L42" s="20"/>
       <c r="M42" s="20"/>
       <c r="N42" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B42, $C$2:$C$911, C42, $D$2:$D$911, D42, $E$2:$E$911, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="20"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -3129,12 +3127,12 @@
       <c r="L43" s="20"/>
       <c r="M43" s="20"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B43, $C$2:$C$911, C43, $D$2:$D$911, D43, $E$2:$E$911, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="20"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -3176,12 +3174,12 @@
         <v>300</v>
       </c>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B44, $C$2:$C$911, C44, $D$2:$D$911, D44, $E$2:$E$911, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="21"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>62</v>
       </c>
@@ -3214,12 +3212,12 @@
       <c r="L45" s="20"/>
       <c r="M45" s="20"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B45, $C$2:$C$911, C45, $D$2:$D$911, D45, $E$2:$E$911, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="20"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>46252.6875</v>
       </c>
@@ -3254,12 +3252,12 @@
       <c r="L46" s="20"/>
       <c r="M46" s="20"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B46, $C$2:$C$911, C46, $D$2:$D$911, D46, $E$2:$E$911, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="20"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>46252.6875</v>
       </c>
@@ -3294,12 +3292,12 @@
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B47, $C$2:$C$911, C47, $D$2:$D$911, D47, $E$2:$E$911, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="20"/>
     </row>
-    <row r="48" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
@@ -3332,12 +3330,12 @@
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B48, $C$2:$C$911, C48, $D$2:$D$911, D48, $E$2:$E$911, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="20"/>
     </row>
-    <row r="49" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>46259.375</v>
       </c>
@@ -3379,12 +3377,12 @@
         <v>260</v>
       </c>
       <c r="N49" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B49, $C$2:$C$911, C49, $D$2:$D$911, D49, $E$2:$E$911, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="21"/>
     </row>
-    <row r="50" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3419,12 +3417,12 @@
       <c r="L50" s="20"/>
       <c r="M50" s="20"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B50, $C$2:$C$911, C50, $D$2:$D$911, D50, $E$2:$E$911, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="20"/>
     </row>
-    <row r="51" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3459,12 +3457,12 @@
       <c r="L51" s="20"/>
       <c r="M51" s="20"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B51, $C$2:$C$911, C51, $D$2:$D$911, D51, $E$2:$E$911, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="20"/>
     </row>
-    <row r="52" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
@@ -3497,12 +3495,12 @@
       <c r="L52" s="20"/>
       <c r="M52" s="20"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B52, $C$2:$C$911, C52, $D$2:$D$911, D52, $E$2:$E$911, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="20"/>
     </row>
-    <row r="53" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
@@ -3535,12 +3533,12 @@
       <c r="L53" s="20"/>
       <c r="M53" s="20"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B53, $C$2:$C$911, C53, $D$2:$D$911, D53, $E$2:$E$911, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53" s="20"/>
     </row>
-    <row r="54" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -3573,12 +3571,12 @@
       <c r="L54" s="20"/>
       <c r="M54" s="20"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B54, $C$2:$C$911, C54, $D$2:$D$911, D54, $E$2:$E$911, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="20"/>
     </row>
-    <row r="55" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -3620,12 +3618,12 @@
         <v>300</v>
       </c>
       <c r="N55" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B55, $C$2:$C$911, C55, $D$2:$D$911, D55, $E$2:$E$911, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="21"/>
     </row>
-    <row r="56" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>46260.375543981485</v>
       </c>
@@ -3667,12 +3665,12 @@
         <v>680</v>
       </c>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B56, $C$2:$C$911, C56, $D$2:$D$911, D56, $E$2:$E$911, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="21"/>
     </row>
-    <row r="57" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>62</v>
       </c>
@@ -3705,12 +3703,12 @@
       <c r="L57" s="20"/>
       <c r="M57" s="20"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B57, $C$2:$C$911, C57, $D$2:$D$911, D57, $E$2:$E$911, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="20"/>
     </row>
-    <row r="58" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -3743,12 +3741,12 @@
       <c r="L58" s="20"/>
       <c r="M58" s="20"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B58, $C$2:$C$911, C58, $D$2:$D$911, D58, $E$2:$E$911, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58" s="20"/>
     </row>
-    <row r="59" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
@@ -3781,12 +3779,12 @@
       <c r="L59" s="20"/>
       <c r="M59" s="20"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B59, $C$2:$C$911, C59, $D$2:$D$911, D59, $E$2:$E$911, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="20"/>
     </row>
-    <row r="60" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -3819,12 +3817,12 @@
       <c r="L60" s="20"/>
       <c r="M60" s="20"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B60, $C$2:$C$911, C60, $D$2:$D$911, D60, $E$2:$E$911, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="20"/>
     </row>
-    <row r="61" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
@@ -3857,12 +3855,12 @@
       <c r="L61" s="20"/>
       <c r="M61" s="20"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B61, $C$2:$C$911, C61, $D$2:$D$911, D61, $E$2:$E$911, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="20"/>
     </row>
-    <row r="62" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -3904,12 +3902,12 @@
         <v>5888</v>
       </c>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B62, $C$2:$C$911, C62, $D$2:$D$911, D62, $E$2:$E$911, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="21"/>
     </row>
-    <row r="63" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
@@ -3942,12 +3940,12 @@
       <c r="L63" s="20"/>
       <c r="M63" s="20"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B63, $C$2:$C$911, C63, $D$2:$D$911, D63, $E$2:$E$911, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="20"/>
     </row>
-    <row r="64" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>46253.375</v>
       </c>
@@ -3982,12 +3980,12 @@
       <c r="L64" s="20"/>
       <c r="M64" s="20"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B64, $C$2:$C$911, C64, $D$2:$D$911, D64, $E$2:$E$911, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="20"/>
     </row>
-    <row r="65" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
@@ -4020,12 +4018,12 @@
       <c r="L65" s="20"/>
       <c r="M65" s="20"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B65, $C$2:$C$911, C65, $D$2:$D$911, D65, $E$2:$E$911, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="20"/>
     </row>
-    <row r="66" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4060,12 +4058,12 @@
       <c r="L66" s="20"/>
       <c r="M66" s="20"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B66, $C$2:$C$911, C66, $D$2:$D$911, D66, $E$2:$E$911, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$911, B66, $C$2:$C$911, C66, $D$2:$D$911, D66, $E$2:$E$911, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66" s="20"/>
     </row>
-    <row r="67" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>62</v>
       </c>
@@ -4098,12 +4096,12 @@
       <c r="L67" s="20"/>
       <c r="M67" s="20"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B67, $C$2:$C$911, C67, $D$2:$D$911, D67, $E$2:$E$911, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="20"/>
     </row>
-    <row r="68" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
@@ -4136,12 +4134,12 @@
       <c r="L68" s="20"/>
       <c r="M68" s="20"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B68, $C$2:$C$911, C68, $D$2:$D$911, D68, $E$2:$E$911, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="20"/>
     </row>
-    <row r="69" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -4174,12 +4172,12 @@
       <c r="L69" s="20"/>
       <c r="M69" s="20"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B69, $C$2:$C$911, C69, $D$2:$D$911, D69, $E$2:$E$911, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="20"/>
     </row>
-    <row r="70" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>46252.6875</v>
       </c>
@@ -4212,12 +4210,12 @@
       <c r="L70" s="20"/>
       <c r="M70" s="20"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B70, $C$2:$C$911, C70, $D$2:$D$911, D70, $E$2:$E$911, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="20"/>
     </row>
-    <row r="71" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -4254,12 +4252,12 @@
       <c r="L71" s="20"/>
       <c r="M71" s="20"/>
       <c r="N71" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B71, $C$2:$C$911, C71, $D$2:$D$911, D71, $E$2:$E$911, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="20"/>
     </row>
-    <row r="72" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -4292,12 +4290,12 @@
       <c r="L72" s="20"/>
       <c r="M72" s="20"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B72, $C$2:$C$911, C72, $D$2:$D$911, D72, $E$2:$E$911, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="20"/>
     </row>
-    <row r="73" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
@@ -4330,12 +4328,12 @@
       <c r="L73" s="20"/>
       <c r="M73" s="20"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B73, $C$2:$C$911, C73, $D$2:$D$911, D73, $E$2:$E$911, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="20"/>
     </row>
-    <row r="74" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>62</v>
       </c>
@@ -4368,12 +4366,12 @@
       <c r="L74" s="20"/>
       <c r="M74" s="20"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B74, $C$2:$C$911, C74, $D$2:$D$911, D74, $E$2:$E$911, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="20"/>
     </row>
-    <row r="75" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -4408,12 +4406,12 @@
       <c r="L75" s="20"/>
       <c r="M75" s="20"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B75, $C$2:$C$911, C75, $D$2:$D$911, D75, $E$2:$E$911, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="20"/>
     </row>
-    <row r="76" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4448,12 +4446,12 @@
       <c r="L76" s="20"/>
       <c r="M76" s="20"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B76, $C$2:$C$911, C76, $D$2:$D$911, D76, $E$2:$E$911, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="20"/>
     </row>
-    <row r="77" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
@@ -4486,12 +4484,12 @@
       <c r="L77" s="20"/>
       <c r="M77" s="20"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B77, $C$2:$C$911, C77, $D$2:$D$911, D77, $E$2:$E$911, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="20"/>
     </row>
-    <row r="78" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>62</v>
       </c>
@@ -4524,12 +4522,12 @@
       <c r="L78" s="20"/>
       <c r="M78" s="20"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B78, $C$2:$C$911, C78, $D$2:$D$911, D78, $E$2:$E$911, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="20"/>
     </row>
-    <row r="79" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>62</v>
       </c>
@@ -4562,12 +4560,12 @@
       <c r="L79" s="20"/>
       <c r="M79" s="20"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B79, $C$2:$C$911, C79, $D$2:$D$911, D79, $E$2:$E$911, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="20"/>
     </row>
-    <row r="80" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -4609,12 +4607,12 @@
         <v>580</v>
       </c>
       <c r="N80" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B80, $C$2:$C$911, C80, $D$2:$D$911, D80, $E$2:$E$911, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="21"/>
     </row>
-    <row r="81" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
@@ -4647,12 +4645,12 @@
       <c r="L81" s="20"/>
       <c r="M81" s="20"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B81, $C$2:$C$911, C81, $D$2:$D$911, D81, $E$2:$E$911, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="20"/>
     </row>
-    <row r="82" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4687,12 +4685,12 @@
       <c r="L82" s="20"/>
       <c r="M82" s="20"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B82, $C$2:$C$911, C82, $D$2:$D$911, D82, $E$2:$E$911, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="20"/>
     </row>
-    <row r="83" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -4734,12 +4732,12 @@
         <v>300</v>
       </c>
       <c r="N83" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B83, $C$2:$C$911, C83, $D$2:$D$911, D83, $E$2:$E$911, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="21"/>
     </row>
-    <row r="84" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
         <v>62</v>
       </c>
@@ -4772,12 +4770,12 @@
       <c r="L84" s="20"/>
       <c r="M84" s="20"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B84, $C$2:$C$911, C84, $D$2:$D$911, D84, $E$2:$E$911, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="20"/>
     </row>
-    <row r="85" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>62</v>
       </c>
@@ -4810,12 +4808,12 @@
       <c r="L85" s="20"/>
       <c r="M85" s="20"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B85, $C$2:$C$911, C85, $D$2:$D$911, D85, $E$2:$E$911, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="20"/>
     </row>
-    <row r="86" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -4848,12 +4846,12 @@
       <c r="L86" s="20"/>
       <c r="M86" s="20"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B86, $C$2:$C$911, C86, $D$2:$D$911, D86, $E$2:$E$911, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="20"/>
     </row>
-    <row r="87" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -4888,12 +4886,12 @@
       <c r="L87" s="20"/>
       <c r="M87" s="20"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B87, $C$2:$C$911, C87, $D$2:$D$911, D87, $E$2:$E$911, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="20"/>
     </row>
-    <row r="88" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4926,12 +4924,12 @@
       <c r="L88" s="20"/>
       <c r="M88" s="20"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B88, $C$2:$C$911, C88, $D$2:$D$911, D88, $E$2:$E$911, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="20"/>
     </row>
-    <row r="89" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>62</v>
       </c>
@@ -4964,12 +4962,12 @@
       <c r="L89" s="20"/>
       <c r="M89" s="20"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B89, $C$2:$C$911, C89, $D$2:$D$911, D89, $E$2:$E$911, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89" s="20"/>
     </row>
-    <row r="90" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>62</v>
       </c>
@@ -5002,12 +5000,12 @@
       <c r="L90" s="20"/>
       <c r="M90" s="20"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B90, $C$2:$C$911, C90, $D$2:$D$911, D90, $E$2:$E$911, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="20"/>
     </row>
-    <row r="91" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>62</v>
       </c>
@@ -5040,12 +5038,12 @@
       <c r="L91" s="20"/>
       <c r="M91" s="20"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B91, $C$2:$C$911, C91, $D$2:$D$911, D91, $E$2:$E$911, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="20"/>
     </row>
-    <row r="92" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>62</v>
       </c>
@@ -5078,12 +5076,12 @@
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B92, $C$2:$C$911, C92, $D$2:$D$911, D92, $E$2:$E$911, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="20"/>
     </row>
-    <row r="93" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>62</v>
       </c>
@@ -5116,12 +5114,12 @@
       <c r="L93" s="20"/>
       <c r="M93" s="20"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B93, $C$2:$C$911, C93, $D$2:$D$911, D93, $E$2:$E$911, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="20"/>
     </row>
-    <row r="94" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5154,12 +5152,12 @@
       <c r="L94" s="20"/>
       <c r="M94" s="20"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B94, $C$2:$C$911, C94, $D$2:$D$911, D94, $E$2:$E$911, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="20"/>
     </row>
-    <row r="95" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
         <v>46252.6875</v>
       </c>
@@ -5194,12 +5192,12 @@
       <c r="L95" s="20"/>
       <c r="M95" s="20"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B95, $C$2:$C$911, C95, $D$2:$D$911, D95, $E$2:$E$911, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="20"/>
     </row>
-    <row r="96" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>62</v>
       </c>
@@ -5232,12 +5230,12 @@
       <c r="L96" s="20"/>
       <c r="M96" s="20"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B96, $C$2:$C$911, C96, $D$2:$D$911, D96, $E$2:$E$911, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="20"/>
     </row>
-    <row r="97" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
@@ -5270,12 +5268,12 @@
       <c r="L97" s="20"/>
       <c r="M97" s="20"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B97, $C$2:$C$911, C97, $D$2:$D$911, D97, $E$2:$E$911, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="20"/>
     </row>
-    <row r="98" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -5310,12 +5308,12 @@
       <c r="L98" s="20"/>
       <c r="M98" s="20"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B98, $C$2:$C$911, C98, $D$2:$D$911, D98, $E$2:$E$911, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="20"/>
     </row>
-    <row r="99" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5348,12 +5346,12 @@
       <c r="L99" s="20"/>
       <c r="M99" s="20"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B99, $C$2:$C$911, C99, $D$2:$D$911, D99, $E$2:$E$911, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="20"/>
     </row>
-    <row r="100" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="23">
         <v>46255</v>
       </c>
@@ -5395,12 +5393,12 @@
         <v>300</v>
       </c>
       <c r="N100" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B100, $C$2:$C$911, C100, $D$2:$D$911, D100, $E$2:$E$911, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="21"/>
     </row>
-    <row r="101" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
@@ -5433,12 +5431,12 @@
       <c r="L101" s="20"/>
       <c r="M101" s="20"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B101, $C$2:$C$911, C101, $D$2:$D$911, D101, $E$2:$E$911, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="20"/>
     </row>
-    <row r="102" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>62</v>
       </c>
@@ -5471,12 +5469,12 @@
       <c r="L102" s="20"/>
       <c r="M102" s="20"/>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B102, $C$2:$C$911, C102, $D$2:$D$911, D102, $E$2:$E$911, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="20"/>
     </row>
-    <row r="103" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>62</v>
       </c>
@@ -5509,12 +5507,12 @@
       <c r="L103" s="20"/>
       <c r="M103" s="20"/>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B103, $C$2:$C$911, C103, $D$2:$D$911, D103, $E$2:$E$911, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="20"/>
     </row>
-    <row r="104" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
         <v>46252.6875</v>
       </c>
@@ -5547,12 +5545,12 @@
       <c r="L104" s="20"/>
       <c r="M104" s="20"/>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B104, $C$2:$C$911, C104, $D$2:$D$911, D104, $E$2:$E$911, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="20"/>
     </row>
-    <row r="105" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
         <v>62</v>
       </c>
@@ -5585,12 +5583,12 @@
       <c r="L105" s="20"/>
       <c r="M105" s="20"/>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B105, $C$2:$C$911, C105, $D$2:$D$911, D105, $E$2:$E$911, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="20"/>
     </row>
-    <row r="106" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>46253.416666666664</v>
       </c>
@@ -5625,12 +5623,12 @@
       <c r="L106" s="20"/>
       <c r="M106" s="20"/>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B106, $C$2:$C$911, C106, $D$2:$D$911, D106, $E$2:$E$911, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="20"/>
     </row>
-    <row r="107" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5663,12 +5661,12 @@
       <c r="L107" s="20"/>
       <c r="M107" s="20"/>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B107, $C$2:$C$911, C107, $D$2:$D$911, D107, $E$2:$E$911, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="20"/>
     </row>
-    <row r="108" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>46254.375</v>
       </c>
@@ -5705,12 +5703,12 @@
       <c r="L108" s="20"/>
       <c r="M108" s="20"/>
       <c r="N108" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B108, $C$2:$C$911, C108, $D$2:$D$911, D108, $E$2:$E$911, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="20"/>
     </row>
-    <row r="109" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
         <v>62</v>
       </c>
@@ -5743,12 +5741,12 @@
       <c r="L109" s="20"/>
       <c r="M109" s="20"/>
       <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B109, $C$2:$C$911, C109, $D$2:$D$911, D109, $E$2:$E$911, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="20"/>
     </row>
-    <row r="110" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>62</v>
       </c>
@@ -5781,12 +5779,12 @@
       <c r="L110" s="20"/>
       <c r="M110" s="20"/>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B110, $C$2:$C$911, C110, $D$2:$D$911, D110, $E$2:$E$911, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="20"/>
     </row>
-    <row r="111" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>62</v>
       </c>
@@ -5821,12 +5819,12 @@
       <c r="L111" s="20"/>
       <c r="M111" s="20"/>
       <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B111, $C$2:$C$911, C111, $D$2:$D$911, D111, $E$2:$E$911, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="20"/>
     </row>
-    <row r="112" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>62</v>
       </c>
@@ -5859,12 +5857,12 @@
       <c r="L112" s="20"/>
       <c r="M112" s="20"/>
       <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B112, $C$2:$C$911, C112, $D$2:$D$911, D112, $E$2:$E$911, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="20"/>
     </row>
-    <row r="113" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5897,12 +5895,12 @@
       <c r="L113" s="20"/>
       <c r="M113" s="20"/>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B113, $C$2:$C$911, C113, $D$2:$D$911, D113, $E$2:$E$911, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="20"/>
     </row>
-    <row r="114" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5935,12 +5933,12 @@
       <c r="L114" s="20"/>
       <c r="M114" s="20"/>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B114, $C$2:$C$911, C114, $D$2:$D$911, D114, $E$2:$E$911, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="20"/>
     </row>
-    <row r="115" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>46252.6875</v>
       </c>
@@ -5973,12 +5971,12 @@
       <c r="L115" s="20"/>
       <c r="M115" s="20"/>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B115, $C$2:$C$911, C115, $D$2:$D$911, D115, $E$2:$E$911, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="20"/>
     </row>
-    <row r="116" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>62</v>
       </c>
@@ -6011,12 +6009,12 @@
       <c r="L116" s="20"/>
       <c r="M116" s="20"/>
       <c r="N116" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B116, $C$2:$C$911, C116, $D$2:$D$911, D116, $E$2:$E$911, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="20"/>
     </row>
-    <row r="117" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="6" t="s">
         <v>62</v>
       </c>
@@ -6051,12 +6049,12 @@
       <c r="L117" s="20"/>
       <c r="M117" s="20"/>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B117, $C$2:$C$911, C117, $D$2:$D$911, D117, $E$2:$E$911, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="20"/>
     </row>
-    <row r="118" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
         <v>62</v>
       </c>
@@ -6089,12 +6087,12 @@
       <c r="L118" s="20"/>
       <c r="M118" s="20"/>
       <c r="N118" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B118, $C$2:$C$911, C118, $D$2:$D$911, D118, $E$2:$E$911, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="20"/>
     </row>
-    <row r="119" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>62</v>
       </c>
@@ -6127,12 +6125,12 @@
       <c r="L119" s="20"/>
       <c r="M119" s="20"/>
       <c r="N119" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B119, $C$2:$C$911, C119, $D$2:$D$911, D119, $E$2:$E$911, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="20"/>
     </row>
-    <row r="120" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>62</v>
       </c>
@@ -6165,12 +6163,12 @@
       <c r="L120" s="20"/>
       <c r="M120" s="20"/>
       <c r="N120" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B120, $C$2:$C$911, C120, $D$2:$D$911, D120, $E$2:$E$911, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="20"/>
     </row>
-    <row r="121" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>62</v>
       </c>
@@ -6203,12 +6201,12 @@
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B121, $C$2:$C$911, C121, $D$2:$D$911, D121, $E$2:$E$911, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="20"/>
     </row>
-    <row r="122" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>62</v>
       </c>
@@ -6241,12 +6239,12 @@
       <c r="L122" s="20"/>
       <c r="M122" s="20"/>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B122, $C$2:$C$911, C122, $D$2:$D$911, D122, $E$2:$E$911, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="20"/>
     </row>
-    <row r="123" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>62</v>
       </c>
@@ -6279,12 +6277,12 @@
       <c r="L123" s="20"/>
       <c r="M123" s="20"/>
       <c r="N123" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B123, $C$2:$C$911, C123, $D$2:$D$911, D123, $E$2:$E$911, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="20"/>
     </row>
-    <row r="124" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>62</v>
       </c>
@@ -6317,12 +6315,12 @@
       <c r="L124" s="20"/>
       <c r="M124" s="20"/>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B124, $C$2:$C$911, C124, $D$2:$D$911, D124, $E$2:$E$911, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="20"/>
     </row>
-    <row r="125" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
         <v>46252.6875</v>
       </c>
@@ -6357,12 +6355,12 @@
       <c r="L125" s="20"/>
       <c r="M125" s="20"/>
       <c r="N125" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B125, $C$2:$C$911, C125, $D$2:$D$911, D125, $E$2:$E$911, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="20"/>
     </row>
-    <row r="126" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>46252.6875</v>
       </c>
@@ -6395,12 +6393,12 @@
       <c r="L126" s="20"/>
       <c r="M126" s="20"/>
       <c r="N126" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B126, $C$2:$C$911, C126, $D$2:$D$911, D126, $E$2:$E$911, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="20"/>
     </row>
-    <row r="127" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>62</v>
       </c>
@@ -6433,12 +6431,12 @@
       <c r="L127" s="20"/>
       <c r="M127" s="20"/>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B127, $C$2:$C$911, C127, $D$2:$D$911, D127, $E$2:$E$911, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="20"/>
     </row>
-    <row r="128" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>62</v>
       </c>
@@ -6471,12 +6469,12 @@
       <c r="L128" s="20"/>
       <c r="M128" s="20"/>
       <c r="N128" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B128, $C$2:$C$911, C128, $D$2:$D$911, D128, $E$2:$E$911, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="20"/>
     </row>
-    <row r="129" spans="1:15" s="32" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:15" s="32" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>62</v>
       </c>
@@ -6509,12 +6507,12 @@
       <c r="L129" s="20"/>
       <c r="M129" s="20"/>
       <c r="N129" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B129, $C$2:$C$911, C129, $D$2:$D$911, D129, $E$2:$E$911, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="20"/>
     </row>
-    <row r="130" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>62</v>
       </c>
@@ -6547,12 +6545,12 @@
       <c r="L130" s="20"/>
       <c r="M130" s="20"/>
       <c r="N130" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B130, $C$2:$C$911, C130, $D$2:$D$911, D130, $E$2:$E$911, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="2">IF(COUNTIFS( $B$2:$B$911, B130, $C$2:$C$911, C130, $D$2:$D$911, D130, $E$2:$E$911, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="20"/>
     </row>
-    <row r="131" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
         <v>62</v>
       </c>
@@ -6585,12 +6583,12 @@
       <c r="L131" s="20"/>
       <c r="M131" s="20"/>
       <c r="N131" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B131, $C$2:$C$911, C131, $D$2:$D$911, D131, $E$2:$E$911, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="20"/>
     </row>
-    <row r="132" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
         <v>62</v>
       </c>
@@ -6625,12 +6623,12 @@
       <c r="L132" s="20"/>
       <c r="M132" s="20"/>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B132, $C$2:$C$911, C132, $D$2:$D$911, D132, $E$2:$E$911, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="20"/>
     </row>
-    <row r="133" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
         <v>62</v>
       </c>
@@ -6665,12 +6663,12 @@
       <c r="L133" s="20"/>
       <c r="M133" s="20"/>
       <c r="N133" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B133, $C$2:$C$911, C133, $D$2:$D$911, D133, $E$2:$E$911, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="20"/>
     </row>
-    <row r="134" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>62</v>
       </c>
@@ -6703,12 +6701,12 @@
       <c r="L134" s="20"/>
       <c r="M134" s="20"/>
       <c r="N134" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B134, $C$2:$C$911, C134, $D$2:$D$911, D134, $E$2:$E$911, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="20"/>
     </row>
-    <row r="135" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="6" t="s">
         <v>62</v>
       </c>
@@ -6741,12 +6739,12 @@
       <c r="L135" s="20"/>
       <c r="M135" s="20"/>
       <c r="N135" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B135, $C$2:$C$911, C135, $D$2:$D$911, D135, $E$2:$E$911, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="20"/>
     </row>
-    <row r="136" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="6" t="s">
         <v>62</v>
       </c>
@@ -6781,12 +6779,12 @@
       <c r="L136" s="20"/>
       <c r="M136" s="20"/>
       <c r="N136" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B136, $C$2:$C$911, C136, $D$2:$D$911, D136, $E$2:$E$911, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="20"/>
     </row>
-    <row r="137" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -6819,12 +6817,12 @@
       <c r="L137" s="20"/>
       <c r="M137" s="20"/>
       <c r="N137" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B137, $C$2:$C$911, C137, $D$2:$D$911, D137, $E$2:$E$911, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="20"/>
     </row>
-    <row r="138" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
         <v>62</v>
       </c>
@@ -6857,12 +6855,12 @@
       <c r="L138" s="20"/>
       <c r="M138" s="20"/>
       <c r="N138" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B138, $C$2:$C$911, C138, $D$2:$D$911, D138, $E$2:$E$911, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="20"/>
     </row>
-    <row r="139" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="6" t="s">
         <v>62</v>
       </c>
@@ -6895,12 +6893,12 @@
       <c r="L139" s="20"/>
       <c r="M139" s="20"/>
       <c r="N139" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B139, $C$2:$C$911, C139, $D$2:$D$911, D139, $E$2:$E$911, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="20"/>
     </row>
-    <row r="140" spans="1:15" s="22" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:15" s="22" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
         <v>62</v>
       </c>
@@ -6933,12 +6931,12 @@
       <c r="L140" s="20"/>
       <c r="M140" s="20"/>
       <c r="N140" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B140, $C$2:$C$911, C140, $D$2:$D$911, D140, $E$2:$E$911, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="20"/>
     </row>
-    <row r="141" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="6" t="s">
         <v>62</v>
       </c>
@@ -6971,12 +6969,12 @@
       <c r="L141" s="20"/>
       <c r="M141" s="20"/>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B141, $C$2:$C$911, C141, $D$2:$D$911, D141, $E$2:$E$911, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="20"/>
     </row>
-    <row r="142" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>62</v>
       </c>
@@ -7011,11 +7009,11 @@
       <c r="L142" s="20"/>
       <c r="M142" s="20"/>
       <c r="N142" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B142, $C$2:$C$911, C142, $D$2:$D$911, D142, $E$2:$E$911, E142) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>62</v>
       </c>
@@ -7048,12 +7046,12 @@
       <c r="L143" s="20"/>
       <c r="M143" s="20"/>
       <c r="N143" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B143, $C$2:$C$911, C143, $D$2:$D$911, D143, $E$2:$E$911, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="20"/>
     </row>
-    <row r="144" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -7086,12 +7084,12 @@
       <c r="L144" s="20"/>
       <c r="M144" s="20"/>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B144, $C$2:$C$911, C144, $D$2:$D$911, D144, $E$2:$E$911, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="20"/>
     </row>
-    <row r="145" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
         <v>62</v>
       </c>
@@ -7124,12 +7122,12 @@
       <c r="L145" s="20"/>
       <c r="M145" s="20"/>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B145, $C$2:$C$911, C145, $D$2:$D$911, D145, $E$2:$E$911, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="20"/>
     </row>
-    <row r="146" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>62</v>
       </c>
@@ -7162,11 +7160,11 @@
       <c r="L146" s="20"/>
       <c r="M146" s="20"/>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B146, $C$2:$C$911, C146, $D$2:$D$911, D146, $E$2:$E$911, E146) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>62</v>
       </c>
@@ -7199,11 +7197,11 @@
       <c r="L147" s="20"/>
       <c r="M147" s="20"/>
       <c r="N147" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B147, $C$2:$C$911, C147, $D$2:$D$911, D147, $E$2:$E$911, E147) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="6" t="s">
         <v>62</v>
       </c>
@@ -7236,12 +7234,12 @@
       <c r="L148" s="20"/>
       <c r="M148" s="20"/>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B148, $C$2:$C$911, C148, $D$2:$D$911, D148, $E$2:$E$911, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="20"/>
     </row>
-    <row r="149" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
         <v>62</v>
       </c>
@@ -7274,11 +7272,11 @@
       <c r="L149" s="20"/>
       <c r="M149" s="20"/>
       <c r="N149" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B149, $C$2:$C$911, C149, $D$2:$D$911, D149, $E$2:$E$911, E149) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>62</v>
       </c>
@@ -7313,11 +7311,11 @@
       <c r="L150" s="20"/>
       <c r="M150" s="20"/>
       <c r="N150" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B150, $C$2:$C$911, C150, $D$2:$D$911, D150, $E$2:$E$911, E150) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
         <v>62</v>
       </c>
@@ -7349,11 +7347,11 @@
         <v>118</v>
       </c>
       <c r="N151" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B151, $C$2:$C$911, C151, $D$2:$D$911, D151, $E$2:$E$911, E151) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="14">
         <v>46253.375</v>
       </c>
@@ -7388,11 +7386,11 @@
         <v>147</v>
       </c>
       <c r="N152" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B152, $C$2:$C$911, C152, $D$2:$D$911, D152, $E$2:$E$911, E152) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -7429,11 +7427,11 @@
       <c r="L153" s="20"/>
       <c r="M153" s="20"/>
       <c r="N153" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B153, $C$2:$C$911, C153, $D$2:$D$911, D153, $E$2:$E$911, E153) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -7475,11 +7473,11 @@
         <v>300</v>
       </c>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B154, $C$2:$C$911, C154, $D$2:$D$911, D154, $E$2:$E$911, E154) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
         <v>46260.375706018516</v>
       </c>
@@ -7521,11 +7519,11 @@
         <v>300</v>
       </c>
       <c r="N155" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B155, $C$2:$C$911, C155, $D$2:$D$911, D155, $E$2:$E$911, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -7555,11 +7553,11 @@
       </c>
       <c r="J156" s="24"/>
       <c r="N156" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B156, $C$2:$C$911, C156, $D$2:$D$911, D156, $E$2:$E$911, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -7591,11 +7589,11 @@
         <v>41</v>
       </c>
       <c r="N157" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B157, $C$2:$C$911, C157, $D$2:$D$911, D157, $E$2:$E$911, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>46260.375659722224</v>
       </c>
@@ -7637,11 +7635,11 @@
         <v>300</v>
       </c>
       <c r="N158" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B158, $C$2:$C$911, C158, $D$2:$D$911, D158, $E$2:$E$911, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -7673,11 +7671,11 @@
         <v>41</v>
       </c>
       <c r="N159" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B159, $C$2:$C$911, C159, $D$2:$D$911, D159, $E$2:$E$911, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="14">
         <v>46252.6875</v>
       </c>
@@ -7709,11 +7707,11 @@
         <v>167</v>
       </c>
       <c r="N160" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B160, $C$2:$C$911, C160, $D$2:$D$911, D160, $E$2:$E$911, E160) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" s="32" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" s="32" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="38">
         <v>46260.634351851855</v>
       </c>
@@ -7755,14 +7753,14 @@
         <v>480</v>
       </c>
       <c r="N161" s="43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B161, $C$2:$C$911, C161, $D$2:$D$911, D161, $E$2:$E$911, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="42" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -7792,11 +7790,11 @@
       </c>
       <c r="J162" s="24"/>
       <c r="N162" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B162, $C$2:$C$911, C162, $D$2:$D$911, D162, $E$2:$E$911, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -7826,12 +7824,12 @@
       </c>
       <c r="J163" s="24"/>
       <c r="N163" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B163, $C$2:$C$911, C163, $D$2:$D$911, D163, $E$2:$E$911, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="13"/>
     </row>
-    <row r="164" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="14">
         <v>46252.645833333336</v>
       </c>
@@ -7861,11 +7859,11 @@
       </c>
       <c r="J164" s="24"/>
       <c r="N164" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B164, $C$2:$C$911, C164, $D$2:$D$911, D164, $E$2:$E$911, E164) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="23">
         <v>46255</v>
       </c>
@@ -7907,11 +7905,11 @@
         <v>300</v>
       </c>
       <c r="N165" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B165, $C$2:$C$911, C165, $D$2:$D$911, D165, $E$2:$E$911, E165) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" s="52" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" s="52" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="44">
         <v>46260.425902777781</v>
       </c>
@@ -7953,12 +7951,12 @@
         <v>1000</v>
       </c>
       <c r="N166" s="51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B166, $C$2:$C$911, C166, $D$2:$D$911, D166, $E$2:$E$911, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O166" s="50"/>
     </row>
-    <row r="167" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -7990,11 +7988,11 @@
         <v>117</v>
       </c>
       <c r="N167" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B167, $C$2:$C$911, C167, $D$2:$D$911, D167, $E$2:$E$911, E167) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="14">
         <v>46252.645833333336</v>
       </c>
@@ -8024,11 +8022,11 @@
       </c>
       <c r="J168" s="24"/>
       <c r="N168" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B168, $C$2:$C$911, C168, $D$2:$D$911, D168, $E$2:$E$911, E168) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="14">
         <v>46253.375</v>
       </c>
@@ -8063,11 +8061,11 @@
         <v>146</v>
       </c>
       <c r="N169" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B169, $C$2:$C$911, C169, $D$2:$D$911, D169, $E$2:$E$911, E169) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="14">
         <v>46252.6875</v>
       </c>
@@ -8097,11 +8095,11 @@
       </c>
       <c r="J170" s="24"/>
       <c r="N170" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B170, $C$2:$C$911, C170, $D$2:$D$911, D170, $E$2:$E$911, E170) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
         <v>46260.557557870372</v>
       </c>
@@ -8143,11 +8141,11 @@
         <v>250</v>
       </c>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B171, $C$2:$C$911, C171, $D$2:$D$911, D171, $E$2:$E$911, E171) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -8189,11 +8187,11 @@
         <v>300</v>
       </c>
       <c r="N172" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B172, $C$2:$C$911, C172, $D$2:$D$911, D172, $E$2:$E$911, E172) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
         <v>46259.375</v>
       </c>
@@ -8235,11 +8233,11 @@
         <v>188</v>
       </c>
       <c r="N173" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B173, $C$2:$C$911, C173, $D$2:$D$911, D173, $E$2:$E$911, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="11" t="s">
         <v>62</v>
       </c>
@@ -8271,12 +8269,12 @@
         <v>117</v>
       </c>
       <c r="N174" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B174, $C$2:$C$911, C174, $D$2:$D$911, D174, $E$2:$E$911, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="13"/>
     </row>
-    <row r="175" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -8308,11 +8306,11 @@
         <v>118</v>
       </c>
       <c r="N175" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B175, $C$2:$C$911, C175, $D$2:$D$911, D175, $E$2:$E$911, E175) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -8342,12 +8340,12 @@
       </c>
       <c r="J176" s="24"/>
       <c r="N176" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B176, $C$2:$C$911, C176, $D$2:$D$911, D176, $E$2:$E$911, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="13"/>
     </row>
-    <row r="177" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -8377,11 +8375,11 @@
       </c>
       <c r="J177" s="24"/>
       <c r="N177" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B177, $C$2:$C$911, C177, $D$2:$D$911, D177, $E$2:$E$911, E177) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" s="32" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" s="32" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -8423,12 +8421,12 @@
         <v>940</v>
       </c>
       <c r="N178" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B178, $C$2:$C$911, C178, $D$2:$D$911, D178, $E$2:$E$911, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="21"/>
     </row>
-    <row r="179" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="23">
         <v>46255</v>
       </c>
@@ -8470,11 +8468,11 @@
         <v>657</v>
       </c>
       <c r="N179" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B179, $C$2:$C$911, C179, $D$2:$D$911, D179, $E$2:$E$911, E179) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -8506,12 +8504,12 @@
         <v>118</v>
       </c>
       <c r="N180" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B180, $C$2:$C$911, C180, $D$2:$D$911, D180, $E$2:$E$911, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="13"/>
     </row>
-    <row r="181" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="14">
         <v>46252.6875</v>
       </c>
@@ -8543,11 +8541,11 @@
         <v>117</v>
       </c>
       <c r="N181" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B181, $C$2:$C$911, C181, $D$2:$D$911, D181, $E$2:$E$911, E181) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="14">
         <v>46252.6875</v>
       </c>
@@ -8579,11 +8577,11 @@
         <v>117</v>
       </c>
       <c r="N182" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B182, $C$2:$C$911, C182, $D$2:$D$911, D182, $E$2:$E$911, E182) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="11" t="s">
         <v>62</v>
       </c>
@@ -8613,11 +8611,11 @@
       </c>
       <c r="J183" s="24"/>
       <c r="N183" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B183, $C$2:$C$911, C183, $D$2:$D$911, D183, $E$2:$E$911, E183) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3">
         <v>46260.555173611108</v>
       </c>
@@ -8659,11 +8657,11 @@
         <v>250</v>
       </c>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B184, $C$2:$C$911, C184, $D$2:$D$911, D184, $E$2:$E$911, E184) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -8695,11 +8693,11 @@
         <v>117</v>
       </c>
       <c r="N185" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B185, $C$2:$C$911, C185, $D$2:$D$911, D185, $E$2:$E$911, E185) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
         <v>46258.443749999999</v>
       </c>
@@ -8741,11 +8739,11 @@
         <v>527.5</v>
       </c>
       <c r="N186" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B186, $C$2:$C$911, C186, $D$2:$D$911, D186, $E$2:$E$911, E186) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="14">
         <v>46253.4</v>
       </c>
@@ -8780,11 +8778,11 @@
         <v>144</v>
       </c>
       <c r="N187" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B187, $C$2:$C$911, C187, $D$2:$D$911, D187, $E$2:$E$911, E187) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="11" t="s">
         <v>62</v>
       </c>
@@ -8816,12 +8814,12 @@
         <v>118</v>
       </c>
       <c r="N188" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B188, $C$2:$C$911, C188, $D$2:$D$911, D188, $E$2:$E$911, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O188" s="13"/>
     </row>
-    <row r="189" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -8853,12 +8851,12 @@
         <v>118</v>
       </c>
       <c r="N189" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B189, $C$2:$C$911, C189, $D$2:$D$911, D189, $E$2:$E$911, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="13"/>
     </row>
-    <row r="190" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -8888,12 +8886,12 @@
       </c>
       <c r="J190" s="24"/>
       <c r="N190" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B190, $C$2:$C$911, C190, $D$2:$D$911, D190, $E$2:$E$911, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="13"/>
     </row>
-    <row r="191" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="11" t="s">
         <v>62</v>
       </c>
@@ -8925,12 +8923,12 @@
         <v>118</v>
       </c>
       <c r="N191" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B191, $C$2:$C$911, C191, $D$2:$D$911, D191, $E$2:$E$911, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="13"/>
     </row>
-    <row r="192" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="11" t="s">
         <v>62</v>
       </c>
@@ -8962,11 +8960,11 @@
         <v>55</v>
       </c>
       <c r="N192" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B192, $C$2:$C$911, C192, $D$2:$D$911, D192, $E$2:$E$911, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
         <v>46260.375671296293</v>
       </c>
@@ -9008,11 +9006,11 @@
         <v>800</v>
       </c>
       <c r="N193" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B193, $C$2:$C$911, C193, $D$2:$D$911, D193, $E$2:$E$911, E193) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="3">
         <v>46259.375</v>
       </c>
@@ -9054,11 +9052,11 @@
         <v>250</v>
       </c>
       <c r="N194" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B194, $C$2:$C$911, C194, $D$2:$D$911, D194, $E$2:$E$911, E194) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="N194:N257" si="3">IF(COUNTIFS( $B$2:$B$911, B194, $C$2:$C$911, C194, $D$2:$D$911, D194, $E$2:$E$911, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
         <v>46260.558067129627</v>
       </c>
@@ -9100,11 +9098,11 @@
         <v>250</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B195, $C$2:$C$911, C195, $D$2:$D$911, D195, $E$2:$E$911, E195) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="14">
         <v>46252.6875</v>
       </c>
@@ -9136,12 +9134,12 @@
         <v>41</v>
       </c>
       <c r="N196" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B196, $C$2:$C$911, C196, $D$2:$D$911, D196, $E$2:$E$911, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="13"/>
     </row>
-    <row r="197" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="14">
         <v>46252.6875</v>
       </c>
@@ -9173,11 +9171,11 @@
         <v>55</v>
       </c>
       <c r="N197" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B197, $C$2:$C$911, C197, $D$2:$D$911, D197, $E$2:$E$911, E197) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="11" t="s">
         <v>62</v>
       </c>
@@ -9207,12 +9205,12 @@
       </c>
       <c r="J198" s="24"/>
       <c r="N198" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B198, $C$2:$C$911, C198, $D$2:$D$911, D198, $E$2:$E$911, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="13"/>
     </row>
-    <row r="199" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -9242,12 +9240,12 @@
       </c>
       <c r="J199" s="24"/>
       <c r="N199" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B199, $C$2:$C$911, C199, $D$2:$D$911, D199, $E$2:$E$911, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="13"/>
     </row>
-    <row r="200" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -9279,11 +9277,11 @@
         <v>55</v>
       </c>
       <c r="N200" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B200, $C$2:$C$911, C200, $D$2:$D$911, D200, $E$2:$E$911, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
         <v>46260.55133101852</v>
       </c>
@@ -9325,11 +9323,11 @@
         <v>300</v>
       </c>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B201, $C$2:$C$911, C201, $D$2:$D$911, D201, $E$2:$E$911, E201) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15" s="32" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" s="32" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="38">
         <v>46259.375</v>
       </c>
@@ -9371,14 +9369,14 @@
         <v>650</v>
       </c>
       <c r="N202" s="32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B202, $C$2:$C$911, C202, $D$2:$D$911, D202, $E$2:$E$911, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="42" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="203" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="11" t="s">
         <v>62</v>
       </c>
@@ -9408,12 +9406,12 @@
       </c>
       <c r="J203" s="24"/>
       <c r="N203" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B203, $C$2:$C$911, C203, $D$2:$D$911, D203, $E$2:$E$911, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="13"/>
     </row>
-    <row r="204" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="11" t="s">
         <v>62</v>
       </c>
@@ -9443,12 +9441,12 @@
       </c>
       <c r="J204" s="24"/>
       <c r="N204" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B204, $C$2:$C$911, C204, $D$2:$D$911, D204, $E$2:$E$911, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="13"/>
     </row>
-    <row r="205" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3">
         <v>46260.375636574077</v>
       </c>
@@ -9490,11 +9488,11 @@
         <v>650</v>
       </c>
       <c r="N205" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B205, $C$2:$C$911, C205, $D$2:$D$911, D205, $E$2:$E$911, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="14">
         <v>46252.6875</v>
       </c>
@@ -9529,12 +9527,12 @@
       <c r="L206" s="21"/>
       <c r="M206" s="21"/>
       <c r="N206" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B206, $C$2:$C$911, C206, $D$2:$D$911, D206, $E$2:$E$911, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="13"/>
     </row>
-    <row r="207" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="14">
         <v>46252.6875</v>
       </c>
@@ -9569,12 +9567,12 @@
       <c r="L207" s="21"/>
       <c r="M207" s="21"/>
       <c r="N207" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B207, $C$2:$C$911, C207, $D$2:$D$911, D207, $E$2:$E$911, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="13"/>
     </row>
-    <row r="208" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="11" t="s">
         <v>62</v>
       </c>
@@ -9609,12 +9607,12 @@
       <c r="L208" s="21"/>
       <c r="M208" s="21"/>
       <c r="N208" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B208, $C$2:$C$911, C208, $D$2:$D$911, D208, $E$2:$E$911, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="13"/>
     </row>
-    <row r="209" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="11" t="s">
         <v>62</v>
       </c>
@@ -9649,12 +9647,12 @@
       <c r="L209" s="21"/>
       <c r="M209" s="21"/>
       <c r="N209" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B209, $C$2:$C$911, C209, $D$2:$D$911, D209, $E$2:$E$911, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="13"/>
     </row>
-    <row r="210" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="11" t="s">
         <v>62</v>
       </c>
@@ -9689,12 +9687,12 @@
       <c r="L210" s="21"/>
       <c r="M210" s="21"/>
       <c r="N210" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B210, $C$2:$C$911, C210, $D$2:$D$911, D210, $E$2:$E$911, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="13"/>
     </row>
-    <row r="211" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="11" t="s">
         <v>62</v>
       </c>
@@ -9727,12 +9725,12 @@
       <c r="L211" s="21"/>
       <c r="M211" s="21"/>
       <c r="N211" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B211, $C$2:$C$911, C211, $D$2:$D$911, D211, $E$2:$E$911, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O211" s="13"/>
     </row>
-    <row r="212" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="11" t="s">
         <v>62</v>
       </c>
@@ -9767,12 +9765,12 @@
       <c r="L212" s="21"/>
       <c r="M212" s="21"/>
       <c r="N212" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B212, $C$2:$C$911, C212, $D$2:$D$911, D212, $E$2:$E$911, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="13"/>
     </row>
-    <row r="213" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -9814,12 +9812,12 @@
         <v>500</v>
       </c>
       <c r="N213" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B213, $C$2:$C$911, C213, $D$2:$D$911, D213, $E$2:$E$911, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="21"/>
     </row>
-    <row r="214" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -9856,12 +9854,12 @@
       <c r="L214" s="21"/>
       <c r="M214" s="21"/>
       <c r="N214" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B214, $C$2:$C$911, C214, $D$2:$D$911, D214, $E$2:$E$911, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="21"/>
     </row>
-    <row r="215" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="14">
         <v>46252.6875</v>
       </c>
@@ -9893,12 +9891,12 @@
         <v>118</v>
       </c>
       <c r="N215" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B215, $C$2:$C$911, C215, $D$2:$D$911, D215, $E$2:$E$911, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="13"/>
     </row>
-    <row r="216" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="11" t="s">
         <v>62</v>
       </c>
@@ -9928,12 +9926,12 @@
       </c>
       <c r="J216" s="37"/>
       <c r="N216" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B216, $C$2:$C$911, C216, $D$2:$D$911, D216, $E$2:$E$911, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="13"/>
     </row>
-    <row r="217" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -9963,12 +9961,12 @@
       </c>
       <c r="J217" s="37"/>
       <c r="N217" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B217, $C$2:$C$911, C217, $D$2:$D$911, D217, $E$2:$E$911, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O217" s="13"/>
     </row>
-    <row r="218" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -10000,12 +9998,12 @@
         <v>118</v>
       </c>
       <c r="N218" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B218, $C$2:$C$911, C218, $D$2:$D$911, D218, $E$2:$E$911, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="13"/>
     </row>
-    <row r="219" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="11" t="s">
         <v>62</v>
       </c>
@@ -10035,11 +10033,11 @@
       </c>
       <c r="J219" s="37"/>
       <c r="N219" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B219, $C$2:$C$911, C219, $D$2:$D$911, D219, $E$2:$E$911, E219) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="220" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="23">
         <v>46255</v>
       </c>
@@ -10081,11 +10079,11 @@
         <v>300</v>
       </c>
       <c r="N220" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B220, $C$2:$C$911, C220, $D$2:$D$911, D220, $E$2:$E$911, E220) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" s="22" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" s="22" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="11" t="s">
         <v>62</v>
       </c>
@@ -10120,12 +10118,12 @@
       <c r="L221" s="21"/>
       <c r="M221" s="21"/>
       <c r="N221" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B221, $C$2:$C$911, C221, $D$2:$D$911, D221, $E$2:$E$911, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="13"/>
     </row>
-    <row r="222" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -10157,12 +10155,12 @@
         <v>55</v>
       </c>
       <c r="N222" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B222, $C$2:$C$911, C222, $D$2:$D$911, D222, $E$2:$E$911, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="13"/>
     </row>
-    <row r="223" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="11" t="s">
         <v>62</v>
       </c>
@@ -10192,12 +10190,12 @@
       </c>
       <c r="J223" s="37"/>
       <c r="N223" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B223, $C$2:$C$911, C223, $D$2:$D$911, D223, $E$2:$E$911, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="13"/>
     </row>
-    <row r="224" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="11" t="s">
         <v>62</v>
       </c>
@@ -10227,12 +10225,12 @@
       </c>
       <c r="J224" s="37"/>
       <c r="N224" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B224, $C$2:$C$911, C224, $D$2:$D$911, D224, $E$2:$E$911, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="13"/>
     </row>
-    <row r="225" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="11" t="s">
         <v>62</v>
       </c>
@@ -10262,12 +10260,12 @@
       </c>
       <c r="J225" s="37"/>
       <c r="N225" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B225, $C$2:$C$911, C225, $D$2:$D$911, D225, $E$2:$E$911, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="13"/>
     </row>
-    <row r="226" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="11" t="s">
         <v>62</v>
       </c>
@@ -10297,12 +10295,12 @@
       </c>
       <c r="J226" s="37"/>
       <c r="N226" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B226, $C$2:$C$911, C226, $D$2:$D$911, D226, $E$2:$E$911, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="13"/>
     </row>
-    <row r="227" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -10334,11 +10332,11 @@
         <v>118</v>
       </c>
       <c r="N227" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B227, $C$2:$C$911, C227, $D$2:$D$911, D227, $E$2:$E$911, E227) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="228" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="11" t="s">
         <v>62</v>
       </c>
@@ -10368,12 +10366,12 @@
       </c>
       <c r="J228" s="37"/>
       <c r="N228" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B228, $C$2:$C$911, C228, $D$2:$D$911, D228, $E$2:$E$911, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="13"/>
     </row>
-    <row r="229" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="11" t="s">
         <v>62</v>
       </c>
@@ -10403,12 +10401,12 @@
       </c>
       <c r="J229" s="37"/>
       <c r="N229" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B229, $C$2:$C$911, C229, $D$2:$D$911, D229, $E$2:$E$911, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="13"/>
     </row>
-    <row r="230" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="11" t="s">
         <v>62</v>
       </c>
@@ -10438,11 +10436,11 @@
       </c>
       <c r="J230" s="37"/>
       <c r="N230" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B230, $C$2:$C$911, C230, $D$2:$D$911, D230, $E$2:$E$911, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="11" t="s">
         <v>62</v>
       </c>
@@ -10474,12 +10472,12 @@
         <v>117</v>
       </c>
       <c r="N231" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B231, $C$2:$C$911, C231, $D$2:$D$911, D231, $E$2:$E$911, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="13"/>
     </row>
-    <row r="232" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="14">
         <v>46253.375</v>
       </c>
@@ -10512,12 +10510,12 @@
         <v>145</v>
       </c>
       <c r="N232" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B232, $C$2:$C$911, C232, $D$2:$D$911, D232, $E$2:$E$911, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="13"/>
     </row>
-    <row r="233" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="11" t="s">
         <v>62</v>
       </c>
@@ -10549,12 +10547,12 @@
         <v>118</v>
       </c>
       <c r="N233" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B233, $C$2:$C$911, C233, $D$2:$D$911, D233, $E$2:$E$911, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O233" s="13"/>
     </row>
-    <row r="234" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="11" t="s">
         <v>62</v>
       </c>
@@ -10584,12 +10582,12 @@
       </c>
       <c r="J234" s="37"/>
       <c r="N234" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B234, $C$2:$C$911, C234, $D$2:$D$911, D234, $E$2:$E$911, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O234" s="13"/>
     </row>
-    <row r="235" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="11" t="s">
         <v>62</v>
       </c>
@@ -10619,12 +10617,12 @@
       </c>
       <c r="J235" s="37"/>
       <c r="N235" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B235, $C$2:$C$911, C235, $D$2:$D$911, D235, $E$2:$E$911, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="13"/>
     </row>
-    <row r="236" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="11" t="s">
         <v>62</v>
       </c>
@@ -10656,12 +10654,12 @@
         <v>118</v>
       </c>
       <c r="N236" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B236, $C$2:$C$911, C236, $D$2:$D$911, D236, $E$2:$E$911, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="13"/>
     </row>
-    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="23">
         <v>46255</v>
       </c>
@@ -10703,11 +10701,11 @@
         <v>300</v>
       </c>
       <c r="N237" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B237, $C$2:$C$911, C237, $D$2:$D$911, D237, $E$2:$E$911, E237) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="238" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="11" t="s">
         <v>62</v>
       </c>
@@ -10737,12 +10735,12 @@
       </c>
       <c r="J238" s="37"/>
       <c r="N238" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B238, $C$2:$C$911, C238, $D$2:$D$911, D238, $E$2:$E$911, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O238" s="13"/>
     </row>
-    <row r="239" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="11" t="s">
         <v>62</v>
       </c>
@@ -10774,12 +10772,12 @@
         <v>117</v>
       </c>
       <c r="N239" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B239, $C$2:$C$911, C239, $D$2:$D$911, D239, $E$2:$E$911, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="13"/>
     </row>
-    <row r="240" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="11" t="s">
         <v>62</v>
       </c>
@@ -10809,12 +10807,12 @@
       </c>
       <c r="J240" s="37"/>
       <c r="N240" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B240, $C$2:$C$911, C240, $D$2:$D$911, D240, $E$2:$E$911, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="13"/>
     </row>
-    <row r="241" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="14">
         <v>46252.6875</v>
       </c>
@@ -10846,11 +10844,11 @@
         <v>118</v>
       </c>
       <c r="N241" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B241, $C$2:$C$911, C241, $D$2:$D$911, D241, $E$2:$E$911, E241) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="242" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="11" t="s">
         <v>62</v>
       </c>
@@ -10880,12 +10878,12 @@
       </c>
       <c r="J242" s="37"/>
       <c r="N242" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B242, $C$2:$C$911, C242, $D$2:$D$911, D242, $E$2:$E$911, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="13"/>
     </row>
-    <row r="243" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="11" t="s">
         <v>62</v>
       </c>
@@ -10915,12 +10913,12 @@
       </c>
       <c r="J243" s="37"/>
       <c r="N243" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B243, $C$2:$C$911, C243, $D$2:$D$911, D243, $E$2:$E$911, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="13"/>
     </row>
-    <row r="244" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="11" t="s">
         <v>62</v>
       </c>
@@ -10952,12 +10950,12 @@
         <v>118</v>
       </c>
       <c r="N244" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B244, $C$2:$C$911, C244, $D$2:$D$911, D244, $E$2:$E$911, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="13"/>
     </row>
-    <row r="245" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="11" t="s">
         <v>62</v>
       </c>
@@ -10987,12 +10985,12 @@
       </c>
       <c r="J245" s="37"/>
       <c r="N245" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B245, $C$2:$C$911, C245, $D$2:$D$911, D245, $E$2:$E$911, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="13"/>
     </row>
-    <row r="246" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="11" t="s">
         <v>62</v>
       </c>
@@ -11022,11 +11020,11 @@
       </c>
       <c r="J246" s="37"/>
       <c r="N246" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B246, $C$2:$C$911, C246, $D$2:$D$911, D246, $E$2:$E$911, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -11068,11 +11066,11 @@
         <v>250</v>
       </c>
       <c r="N247" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B247, $C$2:$C$911, C247, $D$2:$D$911, D247, $E$2:$E$911, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="11" t="s">
         <v>62</v>
       </c>
@@ -11102,11 +11100,11 @@
       </c>
       <c r="J248" s="37"/>
       <c r="N248" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B248, $C$2:$C$911, C248, $D$2:$D$911, D248, $E$2:$E$911, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="11" t="s">
         <v>62</v>
       </c>
@@ -11136,12 +11134,12 @@
       </c>
       <c r="J249" s="37"/>
       <c r="N249" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B249, $C$2:$C$911, C249, $D$2:$D$911, D249, $E$2:$E$911, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="13"/>
     </row>
-    <row r="250" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="11" t="s">
         <v>62</v>
       </c>
@@ -11171,12 +11169,12 @@
       </c>
       <c r="J250" s="37"/>
       <c r="N250" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B250, $C$2:$C$911, C250, $D$2:$D$911, D250, $E$2:$E$911, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="13"/>
     </row>
-    <row r="251" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="11" t="s">
         <v>62</v>
       </c>
@@ -11206,12 +11204,12 @@
       </c>
       <c r="J251" s="37"/>
       <c r="N251" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B251, $C$2:$C$911, C251, $D$2:$D$911, D251, $E$2:$E$911, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="20"/>
     </row>
-    <row r="252" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="11" t="s">
         <v>62</v>
       </c>
@@ -11241,12 +11239,12 @@
       </c>
       <c r="J252" s="37"/>
       <c r="N252" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B252, $C$2:$C$911, C252, $D$2:$D$911, D252, $E$2:$E$911, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="13"/>
     </row>
-    <row r="253" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="11" t="s">
         <v>62</v>
       </c>
@@ -11278,12 +11276,12 @@
         <v>118</v>
       </c>
       <c r="N253" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B253, $C$2:$C$911, C253, $D$2:$D$911, D253, $E$2:$E$911, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="20"/>
     </row>
-    <row r="254" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="11" t="s">
         <v>62</v>
       </c>
@@ -11313,12 +11311,12 @@
       </c>
       <c r="J254" s="37"/>
       <c r="N254" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B254, $C$2:$C$911, C254, $D$2:$D$911, D254, $E$2:$E$911, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="13"/>
     </row>
-    <row r="255" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="11" t="s">
         <v>62</v>
       </c>
@@ -11350,11 +11348,11 @@
         <v>118</v>
       </c>
       <c r="N255" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B255, $C$2:$C$911, C255, $D$2:$D$911, D255, $E$2:$E$911, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
         <v>62</v>
       </c>
@@ -11384,11 +11382,11 @@
       </c>
       <c r="J256" s="37"/>
       <c r="N256" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B256, $C$2:$C$911, C256, $D$2:$D$911, D256, $E$2:$E$911, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="12" t="s">
         <v>62</v>
       </c>
@@ -11418,12 +11416,12 @@
       </c>
       <c r="J257" s="37"/>
       <c r="N257" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B257, $C$2:$C$911, C257, $D$2:$D$911, D257, $E$2:$E$911, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="20"/>
     </row>
-    <row r="258" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
         <v>62</v>
       </c>
@@ -11453,12 +11451,12 @@
       </c>
       <c r="J258" s="37"/>
       <c r="N258" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B258, $C$2:$C$911, C258, $D$2:$D$911, D258, $E$2:$E$911, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N266" si="4">IF(COUNTIFS( $B$2:$B$911, B258, $C$2:$C$911, C258, $D$2:$D$911, D258, $E$2:$E$911, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O258" s="13"/>
     </row>
-    <row r="259" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
         <v>62</v>
       </c>
@@ -11488,12 +11486,12 @@
       </c>
       <c r="J259" s="37"/>
       <c r="N259" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B259, $C$2:$C$911, C259, $D$2:$D$911, D259, $E$2:$E$911, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="20"/>
     </row>
-    <row r="260" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="11" t="s">
         <v>62</v>
       </c>
@@ -11523,12 +11521,12 @@
       </c>
       <c r="J260" s="37"/>
       <c r="N260" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B260, $C$2:$C$911, C260, $D$2:$D$911, D260, $E$2:$E$911, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="13"/>
     </row>
-    <row r="261" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="11" t="s">
         <v>62</v>
       </c>
@@ -11560,12 +11558,12 @@
         <v>118</v>
       </c>
       <c r="N261" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B261, $C$2:$C$911, C261, $D$2:$D$911, D261, $E$2:$E$911, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="20"/>
     </row>
-    <row r="262" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="11" t="s">
         <v>62</v>
       </c>
@@ -11595,12 +11593,12 @@
       </c>
       <c r="J262" s="37"/>
       <c r="N262" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B262, $C$2:$C$911, C262, $D$2:$D$911, D262, $E$2:$E$911, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="20"/>
     </row>
-    <row r="263" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -11642,11 +11640,11 @@
         <v>250</v>
       </c>
       <c r="N263" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B263, $C$2:$C$911, C263, $D$2:$D$911, D263, $E$2:$E$911, E263) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="264" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="11" t="s">
         <v>62</v>
       </c>
@@ -11676,12 +11674,12 @@
       </c>
       <c r="J264" s="37"/>
       <c r="N264" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B264, $C$2:$C$911, C264, $D$2:$D$911, D264, $E$2:$E$911, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="20"/>
     </row>
-    <row r="265" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="14">
         <v>46251.506249999999</v>
       </c>
@@ -11711,12 +11709,12 @@
       </c>
       <c r="J265" s="37"/>
       <c r="N265" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B265, $C$2:$C$911, C265, $D$2:$D$911, D265, $E$2:$E$911, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="20"/>
     </row>
-    <row r="266" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="11" t="s">
         <v>62</v>
       </c>
@@ -11746,45 +11744,30 @@
       </c>
       <c r="J266" s="37"/>
       <c r="N266" s="13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$911, B266, $C$2:$C$911, C266, $D$2:$D$911, D266, $E$2:$E$911, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="20"/>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="N267"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O266" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="GOLDBEESEQ"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O150">
-      <sortCondition descending="1" ref="F1:F266"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.08984375" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" customWidth="1"/>
+    <col min="1" max="1" width="27.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11804,7 +11787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>184</v>
       </c>
@@ -11836,7 +11819,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>185</v>
       </c>
@@ -11868,7 +11851,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>186</v>
       </c>
@@ -11900,7 +11883,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -11932,7 +11915,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>188</v>
       </c>
@@ -11964,7 +11947,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>189</v>
       </c>
@@ -11996,7 +11979,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>190</v>
       </c>
@@ -12028,7 +12011,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>191</v>
       </c>
@@ -12060,7 +12043,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>192</v>
       </c>
@@ -12092,7 +12075,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>193</v>
       </c>
@@ -12124,7 +12107,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>194</v>
       </c>
@@ -12156,7 +12139,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>195</v>
       </c>
@@ -12188,7 +12171,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>196</v>
       </c>
@@ -12220,7 +12203,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>196</v>
       </c>
@@ -12252,7 +12235,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>197</v>
       </c>
@@ -12284,7 +12267,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>197</v>
       </c>
@@ -12316,7 +12299,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>198</v>
       </c>
@@ -12348,7 +12331,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>198</v>
       </c>
@@ -12380,7 +12363,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>198</v>
       </c>
@@ -12412,7 +12395,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>196</v>
       </c>
@@ -12444,7 +12427,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I22" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * :</v>
@@ -12464,27 +12447,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E938BA5-FD24-4E0A-8C6F-17512A252101}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O268"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="13"/>
-    <col min="4" max="5" width="8.90625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="13"/>
-    <col min="10" max="10" width="10.54296875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="13"/>
+    <col min="4" max="5" width="8.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="13" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="13"/>
+    <col min="10" max="10" width="10.5546875" style="21" customWidth="1"/>
     <col min="11" max="11" width="19" style="21" customWidth="1"/>
-    <col min="12" max="13" width="8.90625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.81640625" style="13"/>
-    <col min="15" max="15" width="8.81640625" style="21"/>
-    <col min="16" max="16384" width="8.81640625" style="13"/>
+    <col min="12" max="13" width="8.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="13"/>
+    <col min="15" max="15" width="8.77734375" style="21"/>
+    <col min="16" max="16384" width="8.77734375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -12525,7 +12508,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>62</v>
       </c>
@@ -12563,7 +12546,7 @@
       </c>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>62</v>
       </c>
@@ -12601,7 +12584,7 @@
       </c>
       <c r="O3" s="20"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>46251.506249999999</v>
       </c>
@@ -12639,7 +12622,7 @@
       </c>
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>46259.53266203704</v>
       </c>
@@ -12686,7 +12669,7 @@
       </c>
       <c r="O5" s="21"/>
     </row>
-    <row r="6" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>62</v>
       </c>
@@ -12724,7 +12707,7 @@
       </c>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>62</v>
       </c>
@@ -12764,7 +12747,7 @@
       </c>
       <c r="O7" s="20"/>
     </row>
-    <row r="8" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>62</v>
       </c>
@@ -12802,7 +12785,7 @@
       </c>
       <c r="O8" s="21"/>
     </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>62</v>
       </c>
@@ -12840,7 +12823,7 @@
       </c>
       <c r="O9" s="20"/>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>62</v>
       </c>
@@ -12880,7 +12863,7 @@
       </c>
       <c r="O10" s="20"/>
     </row>
-    <row r="11" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>62</v>
       </c>
@@ -12920,7 +12903,7 @@
       </c>
       <c r="O11" s="21"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>62</v>
       </c>
@@ -12958,7 +12941,7 @@
       </c>
       <c r="O12" s="20"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>62</v>
       </c>
@@ -12996,7 +12979,7 @@
       </c>
       <c r="O13" s="21"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>62</v>
       </c>
@@ -13034,7 +13017,7 @@
       </c>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>46253.375</v>
       </c>
@@ -13074,7 +13057,7 @@
       </c>
       <c r="O15" s="13"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>62</v>
       </c>
@@ -13112,7 +13095,7 @@
       </c>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>62</v>
       </c>
@@ -13150,7 +13133,7 @@
       </c>
       <c r="O17" s="13"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>62</v>
       </c>
@@ -13190,7 +13173,7 @@
       </c>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>62</v>
       </c>
@@ -13228,7 +13211,7 @@
       </c>
       <c r="O19" s="13"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>62</v>
       </c>
@@ -13266,7 +13249,7 @@
       </c>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>62</v>
       </c>
@@ -13304,7 +13287,7 @@
       </c>
       <c r="O21" s="13"/>
     </row>
-    <row r="22" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>62</v>
       </c>
@@ -13342,7 +13325,7 @@
       </c>
       <c r="O22" s="20"/>
     </row>
-    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>62</v>
       </c>
@@ -13380,7 +13363,7 @@
       </c>
       <c r="O23" s="13"/>
     </row>
-    <row r="24" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>62</v>
       </c>
@@ -13420,7 +13403,7 @@
       </c>
       <c r="O24" s="13"/>
     </row>
-    <row r="25" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>62</v>
       </c>
@@ -13458,7 +13441,7 @@
       </c>
       <c r="O25" s="13"/>
     </row>
-    <row r="26" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>62</v>
       </c>
@@ -13496,7 +13479,7 @@
       </c>
       <c r="O26" s="13"/>
     </row>
-    <row r="27" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>62</v>
       </c>
@@ -13536,7 +13519,7 @@
       </c>
       <c r="O27" s="13"/>
     </row>
-    <row r="28" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13583,7 +13566,7 @@
       </c>
       <c r="O28" s="21"/>
     </row>
-    <row r="29" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>62</v>
       </c>
@@ -13621,7 +13604,7 @@
       </c>
       <c r="O29" s="13"/>
     </row>
-    <row r="30" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>62</v>
       </c>
@@ -13659,7 +13642,7 @@
       </c>
       <c r="O30" s="13"/>
     </row>
-    <row r="31" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>62</v>
       </c>
@@ -13697,7 +13680,7 @@
       </c>
       <c r="O31" s="13"/>
     </row>
-    <row r="32" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>62</v>
       </c>
@@ -13735,7 +13718,7 @@
       </c>
       <c r="O32" s="13"/>
     </row>
-    <row r="33" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>62</v>
       </c>
@@ -13773,7 +13756,7 @@
       </c>
       <c r="O33" s="21"/>
     </row>
-    <row r="34" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>62</v>
       </c>
@@ -13811,7 +13794,7 @@
       </c>
       <c r="O34" s="21"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
         <v>62</v>
       </c>
@@ -13849,7 +13832,7 @@
       </c>
       <c r="O35" s="13"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="23">
         <v>46255</v>
       </c>
@@ -13896,7 +13879,7 @@
       </c>
       <c r="O36" s="21"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>62</v>
       </c>
@@ -13936,7 +13919,7 @@
       </c>
       <c r="O37" s="13"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>62</v>
       </c>
@@ -13974,7 +13957,7 @@
       </c>
       <c r="O38" s="13"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
         <v>62</v>
       </c>
@@ -14012,7 +13995,7 @@
       </c>
       <c r="O39" s="13"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
         <v>62</v>
       </c>
@@ -14050,7 +14033,7 @@
       </c>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14">
         <v>46252.6875</v>
       </c>
@@ -14090,7 +14073,7 @@
       </c>
       <c r="O41" s="21"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
         <v>62</v>
       </c>
@@ -14128,7 +14111,7 @@
       </c>
       <c r="O42" s="13"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>62</v>
       </c>
@@ -14166,7 +14149,7 @@
       </c>
       <c r="O43" s="21"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>46259.375138888892</v>
       </c>
@@ -14213,7 +14196,7 @@
       </c>
       <c r="O44" s="21"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14255,7 +14238,7 @@
       </c>
       <c r="O45" s="21"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14295,7 +14278,7 @@
       </c>
       <c r="O46" s="13"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="23">
         <v>46255</v>
       </c>
@@ -14342,7 +14325,7 @@
       </c>
       <c r="O47" s="21"/>
     </row>
-    <row r="48" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -14382,7 +14365,7 @@
       </c>
       <c r="O48" s="21"/>
     </row>
-    <row r="49" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14422,7 +14405,7 @@
       </c>
       <c r="O49" s="13"/>
     </row>
-    <row r="50" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
         <v>62</v>
       </c>
@@ -14462,7 +14445,7 @@
       </c>
       <c r="O50" s="13"/>
     </row>
-    <row r="51" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
         <v>62</v>
       </c>
@@ -14500,7 +14483,7 @@
       </c>
       <c r="O51" s="13"/>
     </row>
-    <row r="52" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
         <v>62</v>
       </c>
@@ -14540,7 +14523,7 @@
       </c>
       <c r="O52" s="13"/>
     </row>
-    <row r="53" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
         <v>62</v>
       </c>
@@ -14578,7 +14561,7 @@
       </c>
       <c r="O53" s="13"/>
     </row>
-    <row r="54" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
         <v>62</v>
       </c>
@@ -14616,7 +14599,7 @@
       </c>
       <c r="O54" s="13"/>
     </row>
-    <row r="55" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14656,7 +14639,7 @@
       </c>
       <c r="O55" s="21"/>
     </row>
-    <row r="56" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
         <v>62</v>
       </c>
@@ -14694,7 +14677,7 @@
       </c>
       <c r="O56" s="13"/>
     </row>
-    <row r="57" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
         <v>46259.375138888892</v>
       </c>
@@ -14741,7 +14724,7 @@
       </c>
       <c r="O57" s="21"/>
     </row>
-    <row r="58" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
         <v>62</v>
       </c>
@@ -14781,7 +14764,7 @@
       </c>
       <c r="O58" s="13"/>
     </row>
-    <row r="59" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14819,7 +14802,7 @@
       </c>
       <c r="O59" s="13"/>
     </row>
-    <row r="60" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -14857,7 +14840,7 @@
       </c>
       <c r="O60" s="13"/>
     </row>
-    <row r="61" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
         <v>62</v>
       </c>
@@ -14897,7 +14880,7 @@
       </c>
       <c r="O61" s="13"/>
     </row>
-    <row r="62" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="14">
         <v>46252.6875</v>
       </c>
@@ -14937,7 +14920,7 @@
       </c>
       <c r="O62" s="13"/>
     </row>
-    <row r="63" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="14">
         <v>46252.6875</v>
       </c>
@@ -14977,7 +14960,7 @@
       </c>
       <c r="O63" s="13"/>
     </row>
-    <row r="64" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
         <v>62</v>
       </c>
@@ -15015,7 +14998,7 @@
       </c>
       <c r="O64" s="13"/>
     </row>
-    <row r="65" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -15062,7 +15045,7 @@
       </c>
       <c r="O65" s="21"/>
     </row>
-    <row r="66" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -15100,7 +15083,7 @@
       </c>
       <c r="O66" s="13"/>
     </row>
-    <row r="67" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>62</v>
       </c>
@@ -15138,7 +15121,7 @@
       </c>
       <c r="O67" s="20"/>
     </row>
-    <row r="68" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -15178,7 +15161,7 @@
       </c>
       <c r="O68" s="21"/>
     </row>
-    <row r="69" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="11" t="s">
         <v>62</v>
       </c>
@@ -15218,7 +15201,7 @@
       </c>
       <c r="O69" s="21"/>
     </row>
-    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="11" t="s">
         <v>62</v>
       </c>
@@ -15258,7 +15241,7 @@
       </c>
       <c r="O70" s="13"/>
     </row>
-    <row r="71" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
         <v>62</v>
       </c>
@@ -15296,7 +15279,7 @@
       </c>
       <c r="O71" s="13"/>
     </row>
-    <row r="72" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -15336,7 +15319,7 @@
       </c>
       <c r="O72" s="13"/>
     </row>
-    <row r="73" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
         <v>62</v>
       </c>
@@ -15374,7 +15357,7 @@
       </c>
       <c r="O73" s="13"/>
     </row>
-    <row r="74" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="14">
         <v>46252.6875</v>
       </c>
@@ -15414,7 +15397,7 @@
       </c>
       <c r="O74" s="13"/>
     </row>
-    <row r="75" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -15454,7 +15437,7 @@
       </c>
       <c r="O75" s="13"/>
     </row>
-    <row r="76" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="11" t="s">
         <v>62</v>
       </c>
@@ -15494,7 +15477,7 @@
       </c>
       <c r="O76" s="13"/>
     </row>
-    <row r="77" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="14">
         <v>46252.6875</v>
       </c>
@@ -15534,7 +15517,7 @@
       </c>
       <c r="O77" s="21"/>
     </row>
-    <row r="78" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="14">
         <v>46252.6875</v>
       </c>
@@ -15574,7 +15557,7 @@
       </c>
       <c r="O78" s="13"/>
     </row>
-    <row r="79" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
         <v>62</v>
       </c>
@@ -15612,7 +15595,7 @@
       </c>
       <c r="O79" s="21"/>
     </row>
-    <row r="80" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -15659,7 +15642,7 @@
       </c>
       <c r="O80" s="21"/>
     </row>
-    <row r="81" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
         <v>46259.375138888892</v>
       </c>
@@ -15706,7 +15689,7 @@
       </c>
       <c r="O81" s="21"/>
     </row>
-    <row r="82" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>46258.443749999999</v>
       </c>
@@ -15753,7 +15736,7 @@
       </c>
       <c r="O82" s="21"/>
     </row>
-    <row r="83" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="14">
         <v>46253.4</v>
       </c>
@@ -15795,7 +15778,7 @@
       </c>
       <c r="O83" s="21"/>
     </row>
-    <row r="84" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -15833,7 +15816,7 @@
       </c>
       <c r="O84" s="13"/>
     </row>
-    <row r="85" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -15873,7 +15856,7 @@
       </c>
       <c r="O85" s="21"/>
     </row>
-    <row r="86" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="14">
         <v>46252.6875</v>
       </c>
@@ -15911,7 +15894,7 @@
       </c>
       <c r="O86" s="21"/>
     </row>
-    <row r="87" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="14">
         <v>46252.6875</v>
       </c>
@@ -15951,7 +15934,7 @@
       </c>
       <c r="O87" s="21"/>
     </row>
-    <row r="88" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="14">
         <v>46252.6875</v>
       </c>
@@ -15991,7 +15974,7 @@
       </c>
       <c r="O88" s="21"/>
     </row>
-    <row r="89" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="11" t="s">
         <v>62</v>
       </c>
@@ -16029,7 +16012,7 @@
       </c>
       <c r="O89" s="13"/>
     </row>
-    <row r="90" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -16067,7 +16050,7 @@
       </c>
       <c r="O90" s="21"/>
     </row>
-    <row r="91" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="14">
         <v>46252.6875</v>
       </c>
@@ -16107,7 +16090,7 @@
       </c>
       <c r="O91" s="21"/>
     </row>
-    <row r="92" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="14">
         <v>46252.688194444447</v>
       </c>
@@ -16145,7 +16128,7 @@
       </c>
       <c r="O92" s="13"/>
     </row>
-    <row r="93" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="23">
         <v>46255</v>
       </c>
@@ -16192,7 +16175,7 @@
       </c>
       <c r="O93" s="21"/>
     </row>
-    <row r="94" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -16232,7 +16215,7 @@
       </c>
       <c r="O94" s="21"/>
     </row>
-    <row r="95" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -16270,7 +16253,7 @@
       </c>
       <c r="O95" s="21"/>
     </row>
-    <row r="96" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="14">
         <v>46252.635416666664</v>
       </c>
@@ -16310,7 +16293,7 @@
       </c>
       <c r="O96" s="21"/>
     </row>
-    <row r="97" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="14">
         <v>46252.645833333336</v>
       </c>
@@ -16348,7 +16331,7 @@
       </c>
       <c r="O97" s="21"/>
     </row>
-    <row r="98" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="23">
         <v>46255</v>
       </c>
@@ -16395,7 +16378,7 @@
       </c>
       <c r="O98" s="21"/>
     </row>
-    <row r="99" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -16437,7 +16420,7 @@
       </c>
       <c r="O99" s="21"/>
     </row>
-    <row r="100" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -16477,7 +16460,7 @@
       </c>
       <c r="O100" s="21"/>
     </row>
-    <row r="101" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="14">
         <v>46253.375</v>
       </c>
@@ -16519,7 +16502,7 @@
       </c>
       <c r="O101" s="21"/>
     </row>
-    <row r="102" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
         <v>46259.38857638889</v>
       </c>
@@ -16566,7 +16549,7 @@
       </c>
       <c r="O102" s="21"/>
     </row>
-    <row r="103" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="11" t="s">
         <v>62</v>
       </c>
@@ -16606,7 +16589,7 @@
       </c>
       <c r="O103" s="13"/>
     </row>
-    <row r="104" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="14">
         <v>46253.375</v>
       </c>
@@ -16648,7 +16631,7 @@
       </c>
       <c r="O104" s="21"/>
     </row>
-    <row r="105" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="14">
         <v>46252.645833333336</v>
       </c>
@@ -16686,7 +16669,7 @@
       </c>
       <c r="O105" s="21"/>
     </row>
-    <row r="106" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="11" t="s">
         <v>62</v>
       </c>
@@ -16726,7 +16709,7 @@
       </c>
       <c r="O106" s="21"/>
     </row>
-    <row r="107" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="14">
         <v>46252.645138888889</v>
       </c>
@@ -16764,7 +16747,7 @@
       </c>
       <c r="O107" s="21"/>
     </row>
-    <row r="108" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
         <v>46252.6875</v>
       </c>
@@ -16804,7 +16787,7 @@
       </c>
       <c r="O108" s="20"/>
     </row>
-    <row r="109" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="23">
         <v>46255</v>
       </c>
@@ -16851,7 +16834,7 @@
       </c>
       <c r="O109" s="21"/>
     </row>
-    <row r="110" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
         <v>46252.6875</v>
       </c>
@@ -16891,7 +16874,7 @@
       </c>
       <c r="O110" s="20"/>
     </row>
-    <row r="111" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
         <v>46252.6875</v>
       </c>
@@ -16929,7 +16912,7 @@
       </c>
       <c r="O111" s="20"/>
     </row>
-    <row r="112" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
         <v>46252.6875</v>
       </c>
@@ -16967,7 +16950,7 @@
       </c>
       <c r="O112" s="20"/>
     </row>
-    <row r="113" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -17005,7 +16988,7 @@
       </c>
       <c r="O113" s="20"/>
     </row>
-    <row r="114" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -17045,7 +17028,7 @@
       </c>
       <c r="O114" s="20"/>
     </row>
-    <row r="115" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -17085,7 +17068,7 @@
       </c>
       <c r="O115" s="20"/>
     </row>
-    <row r="116" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>151</v>
       </c>
@@ -17127,7 +17110,7 @@
       </c>
       <c r="O116" s="20"/>
     </row>
-    <row r="117" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="23">
         <v>46255</v>
       </c>
@@ -17173,7 +17156,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>46252.6875</v>
       </c>
@@ -17211,7 +17194,7 @@
       </c>
       <c r="O118" s="20"/>
     </row>
-    <row r="119" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>62</v>
       </c>
@@ -17251,7 +17234,7 @@
       </c>
       <c r="O119" s="20"/>
     </row>
-    <row r="120" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -17289,7 +17272,7 @@
       </c>
       <c r="O120" s="20"/>
     </row>
-    <row r="121" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>46258.613194444442</v>
       </c>
@@ -17335,7 +17318,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -17381,7 +17364,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>46254.375</v>
       </c>
@@ -17423,7 +17406,7 @@
       </c>
       <c r="O123" s="20"/>
     </row>
-    <row r="124" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
         <v>46252.6875</v>
       </c>
@@ -17461,7 +17444,7 @@
       </c>
       <c r="O124" s="20"/>
     </row>
-    <row r="125" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>62</v>
       </c>
@@ -17499,7 +17482,7 @@
       </c>
       <c r="O125" s="20"/>
     </row>
-    <row r="126" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -17539,7 +17522,7 @@
       </c>
       <c r="O126" s="20"/>
     </row>
-    <row r="127" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -17577,7 +17560,7 @@
       </c>
       <c r="O127" s="20"/>
     </row>
-    <row r="128" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -17617,7 +17600,7 @@
       </c>
       <c r="O128" s="20"/>
     </row>
-    <row r="129" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -17657,7 +17640,7 @@
       </c>
       <c r="O129" s="20"/>
     </row>
-    <row r="130" spans="1:15" s="32" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:15" s="32" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>62</v>
       </c>
@@ -17695,7 +17678,7 @@
       </c>
       <c r="O130" s="20"/>
     </row>
-    <row r="131" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -17735,7 +17718,7 @@
       </c>
       <c r="O131" s="20"/>
     </row>
-    <row r="132" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>46258.459722222222</v>
       </c>
@@ -17781,7 +17764,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -17823,7 +17806,7 @@
       </c>
       <c r="O133" s="20"/>
     </row>
-    <row r="134" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="23">
         <v>46255</v>
       </c>
@@ -17869,7 +17852,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
         <v>46252.6875</v>
       </c>
@@ -17909,7 +17892,7 @@
       </c>
       <c r="O135" s="20"/>
     </row>
-    <row r="136" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -17949,7 +17932,7 @@
       </c>
       <c r="O136" s="20"/>
     </row>
-    <row r="137" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="6" t="s">
         <v>62</v>
       </c>
@@ -17987,7 +17970,7 @@
       </c>
       <c r="O137" s="20"/>
     </row>
-    <row r="138" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
         <v>62</v>
       </c>
@@ -18025,7 +18008,7 @@
       </c>
       <c r="O138" s="20"/>
     </row>
-    <row r="139" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="6" t="s">
         <v>62</v>
       </c>
@@ -18063,7 +18046,7 @@
       </c>
       <c r="O139" s="20"/>
     </row>
-    <row r="140" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
         <v>62</v>
       </c>
@@ -18103,7 +18086,7 @@
       </c>
       <c r="O140" s="20"/>
     </row>
-    <row r="141" spans="1:15" s="22" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:15" s="22" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>46254.375</v>
       </c>
@@ -18145,7 +18128,7 @@
       </c>
       <c r="O141" s="20"/>
     </row>
-    <row r="142" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -18183,7 +18166,7 @@
       </c>
       <c r="O142" s="20"/>
     </row>
-    <row r="143" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>62</v>
       </c>
@@ -18221,7 +18204,7 @@
       </c>
       <c r="O143" s="20"/>
     </row>
-    <row r="144" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>62</v>
       </c>
@@ -18261,7 +18244,7 @@
       </c>
       <c r="O144" s="20"/>
     </row>
-    <row r="145" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
         <v>46252.6875</v>
       </c>
@@ -18301,7 +18284,7 @@
       </c>
       <c r="O145" s="20"/>
     </row>
-    <row r="146" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -18341,7 +18324,7 @@
       </c>
       <c r="O146" s="20"/>
     </row>
-    <row r="147" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>62</v>
       </c>
@@ -18379,7 +18362,7 @@
       </c>
       <c r="O147" s="20"/>
     </row>
-    <row r="148" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -18425,7 +18408,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -18465,7 +18448,7 @@
       </c>
       <c r="O149" s="20"/>
     </row>
-    <row r="150" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>62</v>
       </c>
@@ -18503,7 +18486,7 @@
       </c>
       <c r="O150" s="20"/>
     </row>
-    <row r="151" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
         <v>62</v>
       </c>
@@ -18541,7 +18524,7 @@
       </c>
       <c r="O151" s="20"/>
     </row>
-    <row r="152" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>62</v>
       </c>
@@ -18579,7 +18562,7 @@
       </c>
       <c r="O152" s="20"/>
     </row>
-    <row r="153" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
         <v>46259.375115740739</v>
       </c>
@@ -18625,7 +18608,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -18671,7 +18654,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
         <v>46252.6875</v>
       </c>
@@ -18709,7 +18692,7 @@
       </c>
       <c r="O155" s="20"/>
     </row>
-    <row r="156" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -18747,7 +18730,7 @@
       </c>
       <c r="O156" s="20"/>
     </row>
-    <row r="157" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
         <v>62</v>
       </c>
@@ -18785,7 +18768,7 @@
       </c>
       <c r="O157" s="20"/>
     </row>
-    <row r="158" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -18825,7 +18808,7 @@
       </c>
       <c r="O158" s="20"/>
     </row>
-    <row r="159" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -18863,7 +18846,7 @@
       </c>
       <c r="O159" s="20"/>
     </row>
-    <row r="160" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="6" t="s">
         <v>62</v>
       </c>
@@ -18901,7 +18884,7 @@
       </c>
       <c r="O160" s="20"/>
     </row>
-    <row r="161" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
         <v>62</v>
       </c>
@@ -18939,7 +18922,7 @@
       </c>
       <c r="O161" s="20"/>
     </row>
-    <row r="162" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>62</v>
       </c>
@@ -18977,7 +18960,7 @@
       </c>
       <c r="O162" s="20"/>
     </row>
-    <row r="163" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
         <v>62</v>
       </c>
@@ -19015,7 +18998,7 @@
       </c>
       <c r="O163" s="20"/>
     </row>
-    <row r="164" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>62</v>
       </c>
@@ -19053,7 +19036,7 @@
       </c>
       <c r="O164" s="20"/>
     </row>
-    <row r="165" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -19095,7 +19078,7 @@
       </c>
       <c r="O165" s="20"/>
     </row>
-    <row r="166" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>62</v>
       </c>
@@ -19133,7 +19116,7 @@
       </c>
       <c r="O166" s="20"/>
     </row>
-    <row r="167" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>62</v>
       </c>
@@ -19171,7 +19154,7 @@
       </c>
       <c r="O167" s="20"/>
     </row>
-    <row r="168" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -19217,7 +19200,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="169" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
         <v>46253.375</v>
       </c>
@@ -19257,7 +19240,7 @@
       </c>
       <c r="O169" s="20"/>
     </row>
-    <row r="170" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>62</v>
       </c>
@@ -19295,7 +19278,7 @@
       </c>
       <c r="O170" s="20"/>
     </row>
-    <row r="171" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
         <v>62</v>
       </c>
@@ -19333,7 +19316,7 @@
       </c>
       <c r="O171" s="20"/>
     </row>
-    <row r="172" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>62</v>
       </c>
@@ -19371,7 +19354,7 @@
       </c>
       <c r="O172" s="20"/>
     </row>
-    <row r="173" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
         <v>46253.416666666664</v>
       </c>
@@ -19411,7 +19394,7 @@
       </c>
       <c r="O173" s="20"/>
     </row>
-    <row r="174" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
         <v>46252.6875</v>
       </c>
@@ -19449,7 +19432,7 @@
       </c>
       <c r="O174" s="20"/>
     </row>
-    <row r="175" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
         <v>62</v>
       </c>
@@ -19487,7 +19470,7 @@
       </c>
       <c r="O175" s="20"/>
     </row>
-    <row r="176" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>62</v>
       </c>
@@ -19525,7 +19508,7 @@
       </c>
       <c r="O176" s="20"/>
     </row>
-    <row r="177" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
         <v>62</v>
       </c>
@@ -19563,7 +19546,7 @@
       </c>
       <c r="O177" s="20"/>
     </row>
-    <row r="178" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -19603,7 +19586,7 @@
       </c>
       <c r="O178" s="20"/>
     </row>
-    <row r="179" spans="1:15" s="32" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:15" s="32" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
         <v>46254.375</v>
       </c>
@@ -19645,7 +19628,7 @@
       </c>
       <c r="O179" s="20"/>
     </row>
-    <row r="180" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -19683,7 +19666,7 @@
       </c>
       <c r="O180" s="20"/>
     </row>
-    <row r="181" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -19721,7 +19704,7 @@
       </c>
       <c r="O181" s="20"/>
     </row>
-    <row r="182" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>62</v>
       </c>
@@ -19759,7 +19742,7 @@
       </c>
       <c r="O182" s="20"/>
     </row>
-    <row r="183" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
         <v>62</v>
       </c>
@@ -19797,7 +19780,7 @@
       </c>
       <c r="O183" s="20"/>
     </row>
-    <row r="184" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="7" t="s">
         <v>62</v>
       </c>
@@ -19835,7 +19818,7 @@
       </c>
       <c r="O184" s="20"/>
     </row>
-    <row r="185" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="6" t="s">
         <v>62</v>
       </c>
@@ -19873,7 +19856,7 @@
       </c>
       <c r="O185" s="20"/>
     </row>
-    <row r="186" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="6" t="s">
         <v>62</v>
       </c>
@@ -19911,7 +19894,7 @@
       </c>
       <c r="O186" s="20"/>
     </row>
-    <row r="187" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
         <v>62</v>
       </c>
@@ -19949,7 +19932,7 @@
       </c>
       <c r="O187" s="20"/>
     </row>
-    <row r="188" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>62</v>
       </c>
@@ -19987,7 +19970,7 @@
       </c>
       <c r="O188" s="20"/>
     </row>
-    <row r="189" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
         <v>62</v>
       </c>
@@ -20025,7 +20008,7 @@
       </c>
       <c r="O189" s="20"/>
     </row>
-    <row r="190" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -20063,7 +20046,7 @@
       </c>
       <c r="O190" s="20"/>
     </row>
-    <row r="191" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
         <v>62</v>
       </c>
@@ -20101,7 +20084,7 @@
       </c>
       <c r="O191" s="20"/>
     </row>
-    <row r="192" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -20141,7 +20124,7 @@
       </c>
       <c r="O192" s="20"/>
     </row>
-    <row r="193" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -20181,7 +20164,7 @@
       </c>
       <c r="O193" s="20"/>
     </row>
-    <row r="194" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>62</v>
       </c>
@@ -20219,7 +20202,7 @@
       </c>
       <c r="O194" s="20"/>
     </row>
-    <row r="195" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="3">
         <v>46252.6875</v>
       </c>
@@ -20257,7 +20240,7 @@
       </c>
       <c r="O195" s="20"/>
     </row>
-    <row r="196" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>62</v>
       </c>
@@ -20295,7 +20278,7 @@
       </c>
       <c r="O196" s="20"/>
     </row>
-    <row r="197" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>62</v>
       </c>
@@ -20333,7 +20316,7 @@
       </c>
       <c r="O197" s="20"/>
     </row>
-    <row r="198" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>62</v>
       </c>
@@ -20371,7 +20354,7 @@
       </c>
       <c r="O198" s="20"/>
     </row>
-    <row r="199" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
         <v>62</v>
       </c>
@@ -20409,7 +20392,7 @@
       </c>
       <c r="O199" s="20"/>
     </row>
-    <row r="200" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>62</v>
       </c>
@@ -20447,7 +20430,7 @@
       </c>
       <c r="O200" s="20"/>
     </row>
-    <row r="201" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -20485,7 +20468,7 @@
       </c>
       <c r="O201" s="20"/>
     </row>
-    <row r="202" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3">
         <v>46252.6875</v>
       </c>
@@ -20525,7 +20508,7 @@
       </c>
       <c r="O202" s="20"/>
     </row>
-    <row r="203" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
         <v>62</v>
       </c>
@@ -20563,7 +20546,7 @@
       </c>
       <c r="O203" s="20"/>
     </row>
-    <row r="204" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -20603,7 +20586,7 @@
       </c>
       <c r="O204" s="20"/>
     </row>
-    <row r="205" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
         <v>62</v>
       </c>
@@ -20641,7 +20624,7 @@
       </c>
       <c r="O205" s="20"/>
     </row>
-    <row r="206" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>62</v>
       </c>
@@ -20679,7 +20662,7 @@
       </c>
       <c r="O206" s="20"/>
     </row>
-    <row r="207" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
         <v>62</v>
       </c>
@@ -20717,7 +20700,7 @@
       </c>
       <c r="O207" s="20"/>
     </row>
-    <row r="208" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="23">
         <v>46255</v>
       </c>
@@ -20764,7 +20747,7 @@
       </c>
       <c r="O208" s="21"/>
     </row>
-    <row r="209" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="6" t="s">
         <v>62</v>
       </c>
@@ -20802,7 +20785,7 @@
       </c>
       <c r="O209" s="20"/>
     </row>
-    <row r="210" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>62</v>
       </c>
@@ -20840,7 +20823,7 @@
       </c>
       <c r="O210" s="20"/>
     </row>
-    <row r="211" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
         <v>62</v>
       </c>
@@ -20878,7 +20861,7 @@
       </c>
       <c r="O211" s="20"/>
     </row>
-    <row r="212" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="6" t="s">
         <v>62</v>
       </c>
@@ -20916,7 +20899,7 @@
       </c>
       <c r="O212" s="20"/>
     </row>
-    <row r="213" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
         <v>62</v>
       </c>
@@ -20954,7 +20937,7 @@
       </c>
       <c r="O213" s="20"/>
     </row>
-    <row r="214" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>62</v>
       </c>
@@ -20992,7 +20975,7 @@
       </c>
       <c r="O214" s="20"/>
     </row>
-    <row r="215" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
         <v>62</v>
       </c>
@@ -21032,7 +21015,7 @@
       </c>
       <c r="O215" s="20"/>
     </row>
-    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -21070,7 +21053,7 @@
       </c>
       <c r="O216" s="20"/>
     </row>
-    <row r="217" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
         <v>62</v>
       </c>
@@ -21108,7 +21091,7 @@
       </c>
       <c r="O217" s="20"/>
     </row>
-    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3">
         <v>46252.6875</v>
       </c>
@@ -21146,7 +21129,7 @@
       </c>
       <c r="O218" s="20"/>
     </row>
-    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="6" t="s">
         <v>62</v>
       </c>
@@ -21184,7 +21167,7 @@
       </c>
       <c r="O219" s="20"/>
     </row>
-    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="6" t="s">
         <v>62</v>
       </c>
@@ -21222,7 +21205,7 @@
       </c>
       <c r="O220" s="20"/>
     </row>
-    <row r="221" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3">
         <v>46252.6875</v>
       </c>
@@ -21260,7 +21243,7 @@
       </c>
       <c r="O221" s="20"/>
     </row>
-    <row r="222" spans="1:15" s="22" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:15" s="22" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="6" t="s">
         <v>62</v>
       </c>
@@ -21300,7 +21283,7 @@
       </c>
       <c r="O222" s="20"/>
     </row>
-    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="6" t="s">
         <v>62</v>
       </c>
@@ -21340,7 +21323,7 @@
       </c>
       <c r="O223" s="20"/>
     </row>
-    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="6" t="s">
         <v>62</v>
       </c>
@@ -21378,7 +21361,7 @@
       </c>
       <c r="O224" s="20"/>
     </row>
-    <row r="225" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3">
         <v>46252.6875</v>
       </c>
@@ -21416,7 +21399,7 @@
       </c>
       <c r="O225" s="20"/>
     </row>
-    <row r="226" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="6" t="s">
         <v>62</v>
       </c>
@@ -21454,7 +21437,7 @@
       </c>
       <c r="O226" s="20"/>
     </row>
-    <row r="227" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -21492,7 +21475,7 @@
       </c>
       <c r="O227" s="20"/>
     </row>
-    <row r="228" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="6" t="s">
         <v>62</v>
       </c>
@@ -21530,7 +21513,7 @@
       </c>
       <c r="O228" s="20"/>
     </row>
-    <row r="229" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="6" t="s">
         <v>62</v>
       </c>
@@ -21568,7 +21551,7 @@
       </c>
       <c r="O229" s="20"/>
     </row>
-    <row r="230" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="6" t="s">
         <v>62</v>
       </c>
@@ -21606,7 +21589,7 @@
       </c>
       <c r="O230" s="20"/>
     </row>
-    <row r="231" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="6" t="s">
         <v>62</v>
       </c>
@@ -21644,7 +21627,7 @@
       </c>
       <c r="O231" s="20"/>
     </row>
-    <row r="232" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="6" t="s">
         <v>62</v>
       </c>
@@ -21684,7 +21667,7 @@
       </c>
       <c r="O232" s="20"/>
     </row>
-    <row r="233" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="6" t="s">
         <v>62</v>
       </c>
@@ -21722,7 +21705,7 @@
       </c>
       <c r="O233" s="20"/>
     </row>
-    <row r="234" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="6" t="s">
         <v>62</v>
       </c>
@@ -21762,7 +21745,7 @@
       </c>
       <c r="O234" s="20"/>
     </row>
-    <row r="235" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="6" t="s">
         <v>62</v>
       </c>
@@ -21800,7 +21783,7 @@
       </c>
       <c r="O235" s="20"/>
     </row>
-    <row r="236" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="6" t="s">
         <v>62</v>
       </c>
@@ -21838,7 +21821,7 @@
       </c>
       <c r="O236" s="20"/>
     </row>
-    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="6" t="s">
         <v>62</v>
       </c>
@@ -21876,7 +21859,7 @@
       </c>
       <c r="O237" s="20"/>
     </row>
-    <row r="238" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="6" t="s">
         <v>62</v>
       </c>
@@ -21914,7 +21897,7 @@
       </c>
       <c r="O238" s="20"/>
     </row>
-    <row r="239" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="6" t="s">
         <v>62</v>
       </c>
@@ -21953,7 +21936,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="240" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="6" t="s">
         <v>62</v>
       </c>
@@ -21991,7 +21974,7 @@
       </c>
       <c r="O240" s="20"/>
     </row>
-    <row r="241" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -22029,7 +22012,7 @@
       </c>
       <c r="O241" s="20"/>
     </row>
-    <row r="242" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>62</v>
       </c>
@@ -22066,7 +22049,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="6" t="s">
         <v>62</v>
       </c>
@@ -22103,7 +22086,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="6" t="s">
         <v>62</v>
       </c>
@@ -22141,7 +22124,7 @@
       </c>
       <c r="O244" s="20"/>
     </row>
-    <row r="245" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="6" t="s">
         <v>62</v>
       </c>
@@ -22178,7 +22161,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
         <v>62</v>
       </c>
@@ -22217,7 +22200,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>184</v>
       </c>
@@ -22255,7 +22238,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>185</v>
       </c>
@@ -22293,7 +22276,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>186</v>
       </c>
@@ -22331,7 +22314,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>187</v>
       </c>
@@ -22369,7 +22352,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>188</v>
       </c>
@@ -22407,7 +22390,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>189</v>
       </c>
@@ -22445,7 +22428,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>190</v>
       </c>
@@ -22483,7 +22466,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>191</v>
       </c>
@@ -22521,7 +22504,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>192</v>
       </c>
@@ -22559,7 +22542,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="256" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>193</v>
       </c>
@@ -22597,7 +22580,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>194</v>
       </c>
@@ -22635,7 +22618,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>196</v>
       </c>
@@ -22673,7 +22656,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>196</v>
       </c>
@@ -22711,7 +22694,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>196</v>
       </c>
@@ -22749,7 +22732,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>197</v>
       </c>
@@ -22787,7 +22770,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>197</v>
       </c>
@@ -22825,7 +22808,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>198</v>
       </c>
@@ -22863,7 +22846,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>198</v>
       </c>
@@ -22901,7 +22884,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>198</v>
       </c>
@@ -22939,7 +22922,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>196</v>
       </c>
@@ -22977,7 +22960,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>197</v>
       </c>
@@ -23015,7 +22998,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N268"/>
     </row>
   </sheetData>
